--- a/TestCases_Docs/Bug Report.xlsx
+++ b/TestCases_Docs/Bug Report.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Videos\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CEF578-F64A-4754-B75C-BF1792F68CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576"/>
   </bookViews>
   <sheets>
     <sheet name="Bug Report" sheetId="4" r:id="rId1"/>
@@ -21,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="414">
   <si>
     <t>TesTCASE ID</t>
   </si>
@@ -1530,11 +1524,262 @@
   <si>
     <t>Cart quantity isn't reduced to available stock automatically  when Stock decreases before checkout</t>
   </si>
+  <si>
+    <t>Defect_Admin_001</t>
+  </si>
+  <si>
+    <t>Open URL, Admin is logged in</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> product name: jacket
+ photo: dress.jpg
+ description: olive green jacket
+ price:50 :
+ stock avaliability:2 
+ supplier id: 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.click on actions
+2.click add product
+3.Enter valid product data
+4.Click Save
+</t>
+  </si>
+  <si>
+    <t>jana</t>
+  </si>
+  <si>
+    <t>product list is displayed with product name,decription,  image ,price quantity,supplier id for each product</t>
+  </si>
+  <si>
+    <t>supplier id dosent appear</t>
+  </si>
+  <si>
+    <t>TC-Admin-012</t>
+  </si>
+  <si>
+    <t>SRS-FN-Admin-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the product data in the admin's product page dosent contain supplier id </t>
+  </si>
+  <si>
+    <t>Defect_Admin_002</t>
+  </si>
+  <si>
+    <t>critical</t>
+  </si>
+  <si>
+    <t>TC-Admin-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">admin can't add product with all valid data </t>
+  </si>
+  <si>
+    <t>1.click on actions
+2.click add product
+3.Enter valid product data
+4.Click Save</t>
+  </si>
+  <si>
+    <t>Product is added successfully and redirect admin 
+ to dashboard</t>
+  </si>
+  <si>
+    <t>pop up appear with "please enter valid data"</t>
+  </si>
+  <si>
+    <t>product didn't deleted and pop up message appear 
+"are you sure? "</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product is deleted </t>
+  </si>
+  <si>
+    <t>SRS-FN-Admin-002</t>
+  </si>
+  <si>
+    <t>TC-Admin-003</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>admin can't removeproduct without validation</t>
+  </si>
+  <si>
+    <t>Defect_Admin_003</t>
+  </si>
+  <si>
+    <t>1.click product 
+2.Select product
+3.Click Remove
+4.Confirm deletion</t>
+  </si>
+  <si>
+    <t>Existing product</t>
+  </si>
+  <si>
+    <t>Defect_Admin_004</t>
+  </si>
+  <si>
+    <t>customer did't added but different pop up message appear
+"error creating user"</t>
+  </si>
+  <si>
+    <t>System shows "Email already exists" message and customer account is not created</t>
+  </si>
+  <si>
+    <t>SRS-FN-Admin-003</t>
+  </si>
+  <si>
+    <t>No duplicate customer account is created</t>
+  </si>
+  <si>
+    <t>Product is created</t>
+  </si>
+  <si>
+    <t>Product is deleted</t>
+  </si>
+  <si>
+    <t>1.click on actions section
+ 2.Click Add user
+3.Enter valid Username, existing Email, valid Password, and 4.click on customer radio button
+5.Click Save</t>
+  </si>
+  <si>
+    <t>Existing customer email</t>
+  </si>
+  <si>
+    <t>Open URL, Admin is logged in and a customer account with the same email already exists</t>
+  </si>
+  <si>
+    <t>TC-Admin-006</t>
+  </si>
+  <si>
+    <t>Supplier did't added but different pop up message appear
+"error creating user"</t>
+  </si>
+  <si>
+    <t>System shows "Email already exists" message and supplier account is not created</t>
+  </si>
+  <si>
+    <t>No duplicate supplier account is created</t>
+  </si>
+  <si>
+    <t>1.click on actions section
+ 2.Click Add user
+3.Enter valid Username, existing Email, valid Password, and 4.click on supplier radio button
+5.Click Save</t>
+  </si>
+  <si>
+    <t>Existing supplier email</t>
+  </si>
+  <si>
+    <t>Open URL, Admin is logged in and a supplier account with the same email already exists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">when we add duplicate supplier email unexpected message appear </t>
+  </si>
+  <si>
+    <t xml:space="preserve">when we add duplicate customer email unexpected message appear </t>
+  </si>
+  <si>
+    <t>Defect_Admin_005</t>
+  </si>
+  <si>
+    <t>TC-Admin-009</t>
+  </si>
+  <si>
+    <t>SRS-FN-Admin-004</t>
+  </si>
+  <si>
+    <t>all points appear with these extra points:
+total price and reciever</t>
+  </si>
+  <si>
+    <t>Order list is displayed with Order ID, Customer Name, and Supplier Name for each order</t>
+  </si>
+  <si>
+    <t>SRS-FN-Admin-006</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>Lists remain available for review</t>
+  </si>
+  <si>
+    <t>1.Navigate to dashbord
+2.click orders
+3.validate that all requirments of the order displayed</t>
+  </si>
+  <si>
+    <t>admin see in the order page extra details like total and customer email</t>
+  </si>
+  <si>
+    <t>Defect_Admin_006</t>
+  </si>
+  <si>
+    <t>TC-Admin-013</t>
+  </si>
+  <si>
+    <t>no message 
+appear</t>
+  </si>
+  <si>
+    <t>No product found message is displayed</t>
+  </si>
+  <si>
+    <t>SRS-FN-Admin-008</t>
+  </si>
+  <si>
+    <t>1.click on search bar
+ 2.Enter a non-existing product name in
+3.Click Search button</t>
+  </si>
+  <si>
+    <t>No matching product is displayed</t>
+  </si>
+  <si>
+    <t>Non-existing product name</t>
+  </si>
+  <si>
+    <t>Existing order details</t>
+  </si>
+  <si>
+    <t>when admin search with unavalibale product no message appear</t>
+  </si>
+  <si>
+    <t>Defect_Admin_007</t>
+  </si>
+  <si>
+    <t>TC-Admin-020</t>
+  </si>
+  <si>
+    <t>wireframe</t>
+  </si>
+  <si>
+    <t>there is navbar and footer in pages</t>
+  </si>
+  <si>
+    <t>no navbar and footer in pages</t>
+  </si>
+  <si>
+    <t>1-login with admin account
+2-go to actions (add user page or add products page )or profile page</t>
+  </si>
+  <si>
+    <t>when admin go to add user page , add product page or profile there is navbar and footer in the page</t>
+  </si>
+  <si>
+    <t>Defect_Admin_008</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1818,7 +2063,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2042,12 +2287,330 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{9EE1B2E8-56F1-4388-8F05-1A16A6AD4072}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="49">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2310,7 +2873,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{530EE577-BC47-4F64-BBFD-E7A5116B0BEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -2940,24 +3503,54 @@
       <c r="AE10" s="58"/>
     </row>
     <row r="11" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="61"/>
+      <c r="A11" s="41" t="s">
+        <v>341</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>350</v>
+      </c>
+      <c r="C11" s="61" t="s">
+        <v>342</v>
+      </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="63"/>
+      <c r="E11" s="38" t="s">
+        <v>344</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="78" t="s">
+        <v>16</v>
+      </c>
       <c r="H11" s="68"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="52"/>
+      <c r="I11" s="65" t="s">
+        <v>346</v>
+      </c>
+      <c r="J11" s="52" t="s">
+        <v>347</v>
+      </c>
       <c r="K11" s="56"/>
-      <c r="L11" s="56"/>
-      <c r="M11" s="56"/>
-      <c r="N11" s="56"/>
-      <c r="O11" s="46"/>
-      <c r="P11" s="70"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="71"/>
+      <c r="L11" s="46" t="s">
+        <v>291</v>
+      </c>
+      <c r="M11" s="46" t="s">
+        <v>291</v>
+      </c>
+      <c r="N11" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="O11" s="46" t="s">
+        <v>349</v>
+      </c>
+      <c r="P11" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="R11" s="71" t="s">
+        <v>345</v>
+      </c>
       <c r="S11" s="57"/>
       <c r="T11" s="58"/>
       <c r="U11" s="58"/>
@@ -2973,24 +3566,58 @@
       <c r="AE11" s="58"/>
     </row>
     <row r="12" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="52"/>
+      <c r="A12" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" s="61" t="s">
+        <v>342</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="78" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="81" t="s">
+        <v>372</v>
+      </c>
+      <c r="I12" s="64" t="s">
+        <v>356</v>
+      </c>
+      <c r="J12" s="52" t="s">
+        <v>357</v>
+      </c>
       <c r="K12" s="56"/>
-      <c r="L12" s="56"/>
-      <c r="M12" s="56"/>
-      <c r="N12" s="56"/>
-      <c r="O12" s="46"/>
-      <c r="P12" s="70"/>
-      <c r="Q12" s="72"/>
-      <c r="R12" s="71"/>
+      <c r="L12" s="46" t="s">
+        <v>300</v>
+      </c>
+      <c r="M12" s="46" t="s">
+        <v>352</v>
+      </c>
+      <c r="N12" s="46" t="s">
+        <v>353</v>
+      </c>
+      <c r="O12" s="46" t="s">
+        <v>349</v>
+      </c>
+      <c r="P12" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q12" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="R12" s="71" t="s">
+        <v>345</v>
+      </c>
       <c r="S12" s="57"/>
       <c r="T12" s="58"/>
       <c r="U12" s="58"/>
@@ -3006,24 +3633,58 @@
       <c r="AE12" s="58"/>
     </row>
     <row r="13" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="52"/>
+      <c r="A13" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C13" s="61" t="s">
+        <v>342</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="82" t="s">
+        <v>373</v>
+      </c>
+      <c r="I13" s="64" t="s">
+        <v>359</v>
+      </c>
+      <c r="J13" s="52" t="s">
+        <v>358</v>
+      </c>
       <c r="K13" s="56"/>
-      <c r="L13" s="56"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="56"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="70"/>
-      <c r="Q13" s="72"/>
-      <c r="R13" s="71"/>
+      <c r="L13" s="46" t="s">
+        <v>362</v>
+      </c>
+      <c r="M13" s="46" t="s">
+        <v>362</v>
+      </c>
+      <c r="N13" s="46" t="s">
+        <v>361</v>
+      </c>
+      <c r="O13" s="46" t="s">
+        <v>360</v>
+      </c>
+      <c r="P13" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q13" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="R13" s="71" t="s">
+        <v>345</v>
+      </c>
       <c r="S13" s="57"/>
       <c r="T13" s="58"/>
       <c r="U13" s="58"/>
@@ -3039,24 +3700,58 @@
       <c r="AE13" s="58"/>
     </row>
     <row r="14" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="52"/>
+      <c r="A14" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C14" s="61" t="s">
+        <v>376</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="82" t="s">
+        <v>371</v>
+      </c>
+      <c r="I14" s="64" t="s">
+        <v>369</v>
+      </c>
+      <c r="J14" s="52" t="s">
+        <v>368</v>
+      </c>
       <c r="K14" s="56"/>
-      <c r="L14" s="56"/>
-      <c r="M14" s="56"/>
-      <c r="N14" s="56"/>
-      <c r="O14" s="46"/>
-      <c r="P14" s="70"/>
-      <c r="Q14" s="72"/>
-      <c r="R14" s="71"/>
+      <c r="L14" s="46" t="s">
+        <v>291</v>
+      </c>
+      <c r="M14" s="46" t="s">
+        <v>300</v>
+      </c>
+      <c r="N14" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="O14" s="46" t="s">
+        <v>370</v>
+      </c>
+      <c r="P14" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q14" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="R14" s="71" t="s">
+        <v>345</v>
+      </c>
       <c r="S14" s="57"/>
       <c r="T14" s="58"/>
       <c r="U14" s="58"/>
@@ -3072,24 +3767,58 @@
       <c r="AE14" s="58"/>
     </row>
     <row r="15" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="52"/>
+      <c r="A15" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C15" s="61" t="s">
+        <v>383</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="82" t="s">
+        <v>380</v>
+      </c>
+      <c r="I15" s="64" t="s">
+        <v>379</v>
+      </c>
+      <c r="J15" s="52" t="s">
+        <v>378</v>
+      </c>
       <c r="K15" s="56"/>
-      <c r="L15" s="56"/>
-      <c r="M15" s="56"/>
-      <c r="N15" s="56"/>
-      <c r="O15" s="46"/>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="72"/>
-      <c r="R15" s="71"/>
+      <c r="L15" s="46" t="s">
+        <v>291</v>
+      </c>
+      <c r="M15" s="46" t="s">
+        <v>300</v>
+      </c>
+      <c r="N15" s="46" t="s">
+        <v>387</v>
+      </c>
+      <c r="O15" s="46" t="s">
+        <v>388</v>
+      </c>
+      <c r="P15" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q15" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="R15" s="71" t="s">
+        <v>345</v>
+      </c>
       <c r="S15" s="57"/>
       <c r="T15" s="58"/>
       <c r="U15" s="58"/>
@@ -3105,24 +3834,58 @@
       <c r="AE15" s="58"/>
     </row>
     <row r="16" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="63"/>
-      <c r="H16" s="68"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="52"/>
+      <c r="A16" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C16" s="61" t="s">
+        <v>342</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="81" t="s">
+        <v>393</v>
+      </c>
+      <c r="I16" s="64" t="s">
+        <v>390</v>
+      </c>
+      <c r="J16" s="52" t="s">
+        <v>389</v>
+      </c>
       <c r="K16" s="56"/>
-      <c r="L16" s="56"/>
-      <c r="M16" s="56"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="46"/>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="72"/>
-      <c r="R16" s="71"/>
+      <c r="L16" s="46" t="s">
+        <v>392</v>
+      </c>
+      <c r="M16" s="46" t="s">
+        <v>291</v>
+      </c>
+      <c r="N16" s="46" t="s">
+        <v>397</v>
+      </c>
+      <c r="O16" s="46" t="s">
+        <v>391</v>
+      </c>
+      <c r="P16" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q16" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="R16" s="71" t="s">
+        <v>345</v>
+      </c>
       <c r="S16" s="57"/>
       <c r="T16" s="58"/>
       <c r="U16" s="58"/>
@@ -3138,24 +3901,58 @@
       <c r="AE16" s="58"/>
     </row>
     <row r="17" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="68"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="52"/>
+      <c r="A17" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C17" s="61" t="s">
+        <v>342</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="81" t="s">
+        <v>402</v>
+      </c>
+      <c r="I17" s="64" t="s">
+        <v>399</v>
+      </c>
+      <c r="J17" s="52" t="s">
+        <v>398</v>
+      </c>
       <c r="K17" s="56"/>
-      <c r="L17" s="56"/>
-      <c r="M17" s="56"/>
-      <c r="N17" s="56"/>
-      <c r="O17" s="46"/>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="72"/>
-      <c r="R17" s="71"/>
+      <c r="L17" s="46" t="s">
+        <v>362</v>
+      </c>
+      <c r="M17" s="46" t="s">
+        <v>362</v>
+      </c>
+      <c r="N17" s="46" t="s">
+        <v>407</v>
+      </c>
+      <c r="O17" s="46" t="s">
+        <v>400</v>
+      </c>
+      <c r="P17" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q17" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="R17" s="71" t="s">
+        <v>345</v>
+      </c>
       <c r="S17" s="57"/>
       <c r="T17" s="58"/>
       <c r="U17" s="58"/>
@@ -3171,24 +3968,52 @@
       <c r="AE17" s="58"/>
     </row>
     <row r="18" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="61"/>
+      <c r="A18" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C18" s="61" t="s">
+        <v>342</v>
+      </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="63"/>
+      <c r="E18" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="63" t="s">
+        <v>16</v>
+      </c>
       <c r="H18" s="68"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="52"/>
+      <c r="I18" s="64" t="s">
+        <v>410</v>
+      </c>
+      <c r="J18" s="52" t="s">
+        <v>409</v>
+      </c>
       <c r="K18" s="56"/>
-      <c r="L18" s="56"/>
-      <c r="M18" s="56"/>
+      <c r="L18" s="46" t="s">
+        <v>362</v>
+      </c>
+      <c r="M18" s="46" t="s">
+        <v>362</v>
+      </c>
       <c r="N18" s="56"/>
-      <c r="O18" s="46"/>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="72"/>
-      <c r="R18" s="71"/>
+      <c r="O18" s="46" t="s">
+        <v>408</v>
+      </c>
+      <c r="P18" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q18" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="R18" s="71" t="s">
+        <v>345</v>
+      </c>
       <c r="S18" s="57"/>
       <c r="T18" s="58"/>
       <c r="U18" s="58"/>
@@ -9601,34 +10426,80 @@
     </row>
   </sheetData>
   <phoneticPr fontId="22" type="noConversion"/>
-  <conditionalFormatting sqref="Q2:Q22">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="New">
+  <conditionalFormatting sqref="Q19:Q22 Q2:Q11">
+    <cfRule type="containsText" dxfId="48" priority="15" operator="containsText" text="New">
       <formula>NOT(ISERROR(SEARCH("New",Q2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="New">
+    <cfRule type="containsText" dxfId="47" priority="16" operator="containsText" text="New">
       <formula>NOT(ISERROR(SEARCH("New",Q2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Closed">
+    <cfRule type="containsText" dxfId="46" priority="17" operator="containsText" text="Closed">
       <formula>NOT(ISERROR(SEARCH("Closed",Q2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Fix">
+    <cfRule type="containsText" dxfId="45" priority="18" operator="containsText" text="Fix">
       <formula>NOT(ISERROR(SEARCH("Fix",Q2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Reopen">
+    <cfRule type="containsText" dxfId="44" priority="19" operator="containsText" text="Reopen">
       <formula>NOT(ISERROR(SEARCH("Reopen",Q2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="Open">
+    <cfRule type="containsText" dxfId="43" priority="20" operator="containsText" text="Open">
       <formula>NOT(ISERROR(SEARCH("Open",Q2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="Reopen">
+    <cfRule type="containsText" dxfId="42" priority="21" operator="containsText" text="Reopen">
       <formula>NOT(ISERROR(SEARCH("Reopen",Q2)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q12">
+    <cfRule type="containsText" dxfId="41" priority="8" operator="containsText" text="New">
+      <formula>NOT(ISERROR(SEARCH("New",Q12)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="40" priority="9" operator="containsText" text="New">
+      <formula>NOT(ISERROR(SEARCH("New",Q12)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="39" priority="10" operator="containsText" text="Closed">
+      <formula>NOT(ISERROR(SEARCH("Closed",Q12)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="38" priority="11" operator="containsText" text="Fix">
+      <formula>NOT(ISERROR(SEARCH("Fix",Q12)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="37" priority="12" operator="containsText" text="Reopen">
+      <formula>NOT(ISERROR(SEARCH("Reopen",Q12)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="36" priority="13" operator="containsText" text="Open">
+      <formula>NOT(ISERROR(SEARCH("Open",Q12)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="35" priority="14" operator="containsText" text="Reopen">
+      <formula>NOT(ISERROR(SEARCH("Reopen",Q12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q13:Q18">
+    <cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="New">
+      <formula>NOT(ISERROR(SEARCH("New",Q13)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="33" priority="2" operator="containsText" text="New">
+      <formula>NOT(ISERROR(SEARCH("New",Q13)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="Closed">
+      <formula>NOT(ISERROR(SEARCH("Closed",Q13)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="31" priority="4" operator="containsText" text="Fix">
+      <formula>NOT(ISERROR(SEARCH("Fix",Q13)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="30" priority="5" operator="containsText" text="Reopen">
+      <formula>NOT(ISERROR(SEARCH("Reopen",Q13)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="Open">
+      <formula>NOT(ISERROR(SEARCH("Open",Q13)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="28" priority="7" operator="containsText" text="Reopen">
+      <formula>NOT(ISERROR(SEARCH("Reopen",Q13)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F22" xr:uid="{872A2AB6-2ADB-4D3A-9A56-79D755130126}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F22">
       <formula1>"valid,invalid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q22" xr:uid="{7A9CF52A-021F-4101-8226-913AE7D0D2C0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q22">
       <formula1>"New, Open, Fix, Reopen, Closed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9638,7 +10509,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -15162,20 +16033,20 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q2:Q979" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q2:Q979">
       <formula1>"not executed,blocked,failed,passed"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="E5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="E6" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="E7" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="E8" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="E9" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="E36" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E36" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/TestCases_Docs/Bug Report.xlsx
+++ b/TestCases_Docs/Bug Report.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A439B612-3ECE-42A9-9B6B-2515A1DD1CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576"/>
+    <workbookView xWindow="0" yWindow="900" windowWidth="23040" windowHeight="7044" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bug Report" sheetId="4" r:id="rId1"/>
@@ -15,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="443">
   <si>
     <t>TesTCASE ID</t>
   </si>
@@ -1525,10 +1531,141 @@
     <t>Cart quantity isn't reduced to available stock automatically  when Stock decreases before checkout</t>
   </si>
   <si>
+    <t>Defect_CHK_001</t>
+  </si>
+  <si>
+    <t>Defect_CHK_002</t>
+  </si>
+  <si>
+    <t>Defect_CHK_003</t>
+  </si>
+  <si>
+    <t>Defect_CHK_004</t>
+  </si>
+  <si>
+    <t>Defect_CHK_005</t>
+  </si>
+  <si>
+    <t>Verify City field is mandatory when left empty with other valid data</t>
+  </si>
+  <si>
+    <t>Verify Address field is mandatory when left empty with other valid data</t>
+  </si>
+  <si>
+    <t>Verify successful checkout with valid data
+(city, Address, Mobile phone of reciever, name's reciever, Email)</t>
+  </si>
+  <si>
+    <t>SRS-FN- Checkout-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRS-FN-Checkout-002
+</t>
+  </si>
+  <si>
+    <t>SRS-FN-Checkout-002</t>
+  </si>
+  <si>
+    <t>open URL
+User logged in</t>
+  </si>
+  <si>
+    <t>1. Select product from home page 
+2. Add product to cart
+3. Open cart 
+4. Click checkout
+5. Leave City field empty
+6. Enter Address 
+7. Enter phone of reciever
+8.Enter name of reciever
+9. Click confirm Order button</t>
+  </si>
+  <si>
+    <t>1. Select product from home page 
+2. Add product to cart
+3. Open cart 
+4. Click checkout
+5. Enter City
+6. Leave Address field empty
+7. Enter phone of reciever
+8.Enter name of reciever
+9. Click confirm Order button</t>
+  </si>
+  <si>
+    <t>1. Select product from home page 
+2. Add product to cart
+3. Open cart 
+4. Click checkout
+5. Enter City field 
+6. Enter Address field
+7. Enter phone of reciever
+8.leave name of reciever empty
+9. Click confirm Order button</t>
+  </si>
+  <si>
+    <t>1. Select product from home page 
+2. Add product to cart
+3. Open cart 
+4. Click checkout
+5. Enter City field
+6. Enter Address field
+7. Leave phone of reciever
+8.Enter name of reciever 
+9. Click confirm Order button</t>
+  </si>
+  <si>
+    <t>1. Select product from home page 
+2. Add product to cart
+3. Open cart 
+4. Click checkout
+5. Enter City field 
+6. Enter Address field 
+7. Enter phone of reciever
+8.Enter name of reciever 
+9. Click confirm Order button</t>
+  </si>
+  <si>
+    <t>Verify name of reciever name field is mandatory when left empty with other valid data</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Verify phone of reciever phone field is mandatory when left empty with other valid data</t>
+  </si>
+  <si>
     <t>Defect_Admin_001</t>
   </si>
   <si>
+    <t xml:space="preserve">the product data in the admin's product page dosent contain supplier id </t>
+  </si>
+  <si>
     <t>Open URL, Admin is logged in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.click on actions
+2.click add product
+3.Enter valid product data
+4.Click Save
+</t>
+  </si>
+  <si>
+    <t>product list is displayed with product name,decription,  image ,price quantity,supplier id for each product</t>
+  </si>
+  <si>
+    <t>supplier id dosent appear</t>
+  </si>
+  <si>
+    <t>TC-Admin-012</t>
+  </si>
+  <si>
+    <t>SRS-FN-Admin-001</t>
+  </si>
+  <si>
+    <t>jana</t>
+  </si>
+  <si>
+    <t>Defect_Admin_002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">admin can't add product with all valid data </t>
   </si>
   <si>
     <t xml:space="preserve"> product name: jacket
@@ -1539,49 +1676,15 @@
  supplier id: 16</t>
   </si>
   <si>
-    <t xml:space="preserve">1.click on actions
-2.click add product
-3.Enter valid product data
-4.Click Save
-</t>
-  </si>
-  <si>
-    <t>jana</t>
-  </si>
-  <si>
-    <t>product list is displayed with product name,decription,  image ,price quantity,supplier id for each product</t>
-  </si>
-  <si>
-    <t>supplier id dosent appear</t>
-  </si>
-  <si>
-    <t>TC-Admin-012</t>
-  </si>
-  <si>
-    <t>SRS-FN-Admin-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">the product data in the admin's product page dosent contain supplier id </t>
-  </si>
-  <si>
-    <t>Defect_Admin_002</t>
-  </si>
-  <si>
-    <t>critical</t>
-  </si>
-  <si>
-    <t>TC-Admin-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">admin can't add product with all valid data </t>
-  </si>
-  <si>
     <t>1.click on actions
 2.click add product
 3.Enter valid product data
 4.Click Save</t>
   </si>
   <si>
+    <t>Product is created</t>
+  </si>
+  <si>
     <t>Product is added successfully and redirect admin 
  to dashboard</t>
   </si>
@@ -1589,26 +1692,19 @@
     <t>pop up appear with "please enter valid data"</t>
   </si>
   <si>
-    <t>product didn't deleted and pop up message appear 
-"are you sure? "</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product is deleted </t>
-  </si>
-  <si>
-    <t>SRS-FN-Admin-002</t>
-  </si>
-  <si>
-    <t>TC-Admin-003</t>
-  </si>
-  <si>
-    <t>low</t>
+    <t>critical</t>
+  </si>
+  <si>
+    <t>TC-Admin-01</t>
+  </si>
+  <si>
+    <t>Defect_Admin_003</t>
   </si>
   <si>
     <t>admin can't removeproduct without validation</t>
   </si>
   <si>
-    <t>Defect_Admin_003</t>
+    <t>Existing product</t>
   </si>
   <si>
     <t>1.click product 
@@ -1617,29 +1713,35 @@
 4.Confirm deletion</t>
   </si>
   <si>
-    <t>Existing product</t>
+    <t>Product is deleted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product is deleted </t>
+  </si>
+  <si>
+    <t>product didn't deleted and pop up message appear 
+"are you sure? "</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>TC-Admin-003</t>
+  </si>
+  <si>
+    <t>SRS-FN-Admin-002</t>
   </si>
   <si>
     <t>Defect_Admin_004</t>
   </si>
   <si>
-    <t>customer did't added but different pop up message appear
-"error creating user"</t>
-  </si>
-  <si>
-    <t>System shows "Email already exists" message and customer account is not created</t>
-  </si>
-  <si>
-    <t>SRS-FN-Admin-003</t>
-  </si>
-  <si>
-    <t>No duplicate customer account is created</t>
-  </si>
-  <si>
-    <t>Product is created</t>
-  </si>
-  <si>
-    <t>Product is deleted</t>
+    <t xml:space="preserve">when we add duplicate customer email unexpected message appear </t>
+  </si>
+  <si>
+    <t>Open URL, Admin is logged in and a customer account with the same email already exists</t>
+  </si>
+  <si>
+    <t>Existing customer email</t>
   </si>
   <si>
     <t>1.click on actions section
@@ -1648,23 +1750,32 @@
 5.Click Save</t>
   </si>
   <si>
-    <t>Existing customer email</t>
-  </si>
-  <si>
-    <t>Open URL, Admin is logged in and a customer account with the same email already exists</t>
+    <t>No duplicate customer account is created</t>
+  </si>
+  <si>
+    <t>System shows "Email already exists" message and customer account is not created</t>
+  </si>
+  <si>
+    <t>customer did't added but different pop up message appear
+"error creating user"</t>
   </si>
   <si>
     <t>TC-Admin-006</t>
   </si>
   <si>
-    <t>Supplier did't added but different pop up message appear
-"error creating user"</t>
-  </si>
-  <si>
-    <t>System shows "Email already exists" message and supplier account is not created</t>
-  </si>
-  <si>
-    <t>No duplicate supplier account is created</t>
+    <t>SRS-FN-Admin-003</t>
+  </si>
+  <si>
+    <t>Defect_Admin_005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">when we add duplicate supplier email unexpected message appear </t>
+  </si>
+  <si>
+    <t>Open URL, Admin is logged in and a supplier account with the same email already exists</t>
+  </si>
+  <si>
+    <t>Existing supplier email</t>
   </si>
   <si>
     <t>1.click on actions section
@@ -1673,19 +1784,14 @@
 5.Click Save</t>
   </si>
   <si>
-    <t>Existing supplier email</t>
-  </si>
-  <si>
-    <t>Open URL, Admin is logged in and a supplier account with the same email already exists</t>
-  </si>
-  <si>
-    <t xml:space="preserve">when we add duplicate supplier email unexpected message appear </t>
-  </si>
-  <si>
-    <t xml:space="preserve">when we add duplicate customer email unexpected message appear </t>
-  </si>
-  <si>
-    <t>Defect_Admin_005</t>
+    <t>No duplicate supplier account is created</t>
+  </si>
+  <si>
+    <t>System shows "Email already exists" message and supplier account is not created</t>
+  </si>
+  <si>
+    <t>Supplier did't added but different pop up message appear
+"error creating user"</t>
   </si>
   <si>
     <t>TC-Admin-009</t>
@@ -1694,20 +1800,13 @@
     <t>SRS-FN-Admin-004</t>
   </si>
   <si>
-    <t>all points appear with these extra points:
-total price and reciever</t>
-  </si>
-  <si>
-    <t>Order list is displayed with Order ID, Customer Name, and Supplier Name for each order</t>
-  </si>
-  <si>
-    <t>SRS-FN-Admin-006</t>
-  </si>
-  <si>
-    <t>medium</t>
-  </si>
-  <si>
-    <t>Lists remain available for review</t>
+    <t>Defect_Admin_006</t>
+  </si>
+  <si>
+    <t>admin see in the order page extra details like total and customer email</t>
+  </si>
+  <si>
+    <t>Existing order details</t>
   </si>
   <si>
     <t>1.Navigate to dashbord
@@ -1715,23 +1814,32 @@
 3.validate that all requirments of the order displayed</t>
   </si>
   <si>
-    <t>admin see in the order page extra details like total and customer email</t>
-  </si>
-  <si>
-    <t>Defect_Admin_006</t>
+    <t>Lists remain available for review</t>
+  </si>
+  <si>
+    <t>Order list is displayed with Order ID, Customer Name, and Supplier Name for each order</t>
+  </si>
+  <si>
+    <t>all points appear with these extra points:
+total price and reciever</t>
+  </si>
+  <si>
+    <t>medium</t>
   </si>
   <si>
     <t>TC-Admin-013</t>
   </si>
   <si>
-    <t>no message 
-appear</t>
-  </si>
-  <si>
-    <t>No product found message is displayed</t>
-  </si>
-  <si>
-    <t>SRS-FN-Admin-008</t>
+    <t>SRS-FN-Admin-006</t>
+  </si>
+  <si>
+    <t>Defect_Admin_007</t>
+  </si>
+  <si>
+    <t>when admin search with unavalibale product no message appear</t>
+  </si>
+  <si>
+    <t>Non-existing product name</t>
   </si>
   <si>
     <t>1.click on search bar
@@ -1742,45 +1850,80 @@
     <t>No matching product is displayed</t>
   </si>
   <si>
-    <t>Non-existing product name</t>
-  </si>
-  <si>
-    <t>Existing order details</t>
-  </si>
-  <si>
-    <t>when admin search with unavalibale product no message appear</t>
-  </si>
-  <si>
-    <t>Defect_Admin_007</t>
+    <t>No product found message is displayed</t>
+  </si>
+  <si>
+    <t>no message 
+appear</t>
   </si>
   <si>
     <t>TC-Admin-020</t>
   </si>
   <si>
-    <t>wireframe</t>
-  </si>
-  <si>
-    <t>there is navbar and footer in pages</t>
-  </si>
-  <si>
-    <t>no navbar and footer in pages</t>
+    <t>SRS-FN-Admin-008</t>
+  </si>
+  <si>
+    <t>Defect_Admin_008</t>
+  </si>
+  <si>
+    <t>when admin go to add user page , add product page or profile there is navbar and footer in the page</t>
   </si>
   <si>
     <t>1-login with admin account
 2-go to actions (add user page or add products page )or profile page</t>
   </si>
   <si>
-    <t>when admin go to add user page , add product page or profile there is navbar and footer in the page</t>
-  </si>
-  <si>
-    <t>Defect_Admin_008</t>
+    <t>no navbar and footer in pages</t>
+  </si>
+  <si>
+    <t>there is navbar and footer in pages</t>
+  </si>
+  <si>
+    <t>wireframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user is redirected to home page and pop up message "Order is placed successfully" 
+</t>
+  </si>
+  <si>
+    <t>no popup message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pop up message appears
+"Please Enter the required data"
+ and order is not placed
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no pop up message appears "Please Enter the required data"
+</t>
+  </si>
+  <si>
+    <t>pop up message appears
+"Please Enter the required data"
+ and order is not placed</t>
+  </si>
+  <si>
+    <t>TC_CHK_001</t>
+  </si>
+  <si>
+    <t>TC_CHK_003</t>
+  </si>
+  <si>
+    <t>TC_CHK_004</t>
+  </si>
+  <si>
+    <t>TC_CHK_005</t>
+  </si>
+  <si>
+    <t>TC_CHK_006</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="23" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1916,6 +2059,19 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -2059,11 +2215,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2287,330 +2456,79 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="15">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 10" xfId="9" xr:uid="{832D0BBE-823B-4EE1-8AD4-72D8A89C2F73}"/>
+    <cellStyle name="Normal 11" xfId="10" xr:uid="{3D5C94BC-A247-4B45-917B-A4274E0542D5}"/>
+    <cellStyle name="Normal 12" xfId="11" xr:uid="{3B0A0E51-A249-4CA5-A4DB-F62439F8BB8E}"/>
+    <cellStyle name="Normal 13" xfId="12" xr:uid="{F5408A00-0B76-4E73-8B1E-DDDE739CB25B}"/>
+    <cellStyle name="Normal 14" xfId="13" xr:uid="{57BBBDEB-0AD6-4988-A50D-708126049A8F}"/>
+    <cellStyle name="Normal 15" xfId="14" xr:uid="{6BE7F390-4FE6-4DA2-ABD6-ECE2CE9CD309}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{9EE1B2E8-56F1-4388-8F05-1A16A6AD4072}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{C26CAA55-5F0D-4A90-A11E-A8D20D679B09}"/>
+    <cellStyle name="Normal 4" xfId="3" xr:uid="{A27B9F2B-BBA3-4A08-AF7B-F6CFD0846F73}"/>
+    <cellStyle name="Normal 5" xfId="4" xr:uid="{2A6D86B2-0E2A-4EFB-A8F1-DEBC2095CCFD}"/>
+    <cellStyle name="Normal 6" xfId="5" xr:uid="{793DB909-FCEE-44ED-A466-8993481756E9}"/>
+    <cellStyle name="Normal 7" xfId="6" xr:uid="{D67A7D59-1B8B-437A-AB41-09DDC120947A}"/>
+    <cellStyle name="Normal 8" xfId="7" xr:uid="{459B37FB-7BCD-494F-A52B-7CCE1374E4B9}"/>
+    <cellStyle name="Normal 9" xfId="8" xr:uid="{4CE399EB-C99B-4AC2-AC21-3736EFC3EFB1}"/>
   </cellStyles>
-  <dxfs count="49">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill>
@@ -2873,11 +2791,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{530EE577-BC47-4F64-BBFD-E7A5116B0BEB}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AE1000"/>
+  <dimension ref="A1:AE1007"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.109375" style="45" customWidth="1"/>
@@ -2886,7 +2804,7 @@
     <col min="4" max="4" width="32.6640625" style="45" customWidth="1"/>
     <col min="5" max="5" width="78.109375" style="45" customWidth="1"/>
     <col min="6" max="6" width="24" style="45" customWidth="1"/>
-    <col min="7" max="7" width="22" style="45" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" style="45" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="56.33203125" style="45" customWidth="1"/>
     <col min="9" max="9" width="78.109375" style="45" customWidth="1"/>
     <col min="10" max="10" width="76.6640625" style="45" customWidth="1"/>
@@ -2918,7 +2836,7 @@
       <c r="G1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="95" t="s">
         <v>274</v>
       </c>
       <c r="I1" s="43" t="s">
@@ -3450,7 +3368,7 @@
       <c r="D10" s="76" t="s">
         <v>331</v>
       </c>
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="85" t="s">
         <v>333</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -3504,17 +3422,17 @@
     </row>
     <row r="11" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="41" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="C11" s="61" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="38" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>15</v>
@@ -3524,10 +3442,10 @@
       </c>
       <c r="H11" s="68"/>
       <c r="I11" s="65" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="J11" s="52" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="K11" s="56"/>
       <c r="L11" s="46" t="s">
@@ -3537,10 +3455,10 @@
         <v>291</v>
       </c>
       <c r="N11" s="46" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="O11" s="46" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="P11" s="70" t="s">
         <v>26</v>
@@ -3549,7 +3467,7 @@
         <v>281</v>
       </c>
       <c r="R11" s="71" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="S11" s="57"/>
       <c r="T11" s="58"/>
@@ -3567,19 +3485,19 @@
     </row>
     <row r="12" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="C12" s="61" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>15</v>
@@ -3587,27 +3505,27 @@
       <c r="G12" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="81" t="s">
-        <v>372</v>
+      <c r="H12" s="93" t="s">
+        <v>373</v>
       </c>
       <c r="I12" s="64" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="K12" s="56"/>
       <c r="L12" s="46" t="s">
         <v>300</v>
       </c>
       <c r="M12" s="46" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="N12" s="46" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="O12" s="46" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="P12" s="70" t="s">
         <v>26</v>
@@ -3616,7 +3534,7 @@
         <v>281</v>
       </c>
       <c r="R12" s="71" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="S12" s="57"/>
       <c r="T12" s="58"/>
@@ -3634,19 +3552,19 @@
     </row>
     <row r="13" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="C13" s="61" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>15</v>
@@ -3654,27 +3572,27 @@
       <c r="G13" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="82" t="s">
-        <v>373</v>
+      <c r="H13" s="94" t="s">
+        <v>382</v>
       </c>
       <c r="I13" s="64" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="J13" s="52" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="K13" s="56"/>
       <c r="L13" s="46" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="M13" s="46" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="N13" s="46" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="O13" s="46" t="s">
-        <v>360</v>
+        <v>387</v>
       </c>
       <c r="P13" s="70" t="s">
         <v>26</v>
@@ -3683,7 +3601,7 @@
         <v>281</v>
       </c>
       <c r="R13" s="71" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="S13" s="57"/>
       <c r="T13" s="58"/>
@@ -3701,19 +3619,19 @@
     </row>
     <row r="14" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C14" s="61" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>15</v>
@@ -3721,14 +3639,14 @@
       <c r="G14" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="82" t="s">
-        <v>371</v>
+      <c r="H14" s="94" t="s">
+        <v>393</v>
       </c>
       <c r="I14" s="64" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="J14" s="52" t="s">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="K14" s="56"/>
       <c r="L14" s="46" t="s">
@@ -3738,10 +3656,10 @@
         <v>300</v>
       </c>
       <c r="N14" s="46" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="O14" s="46" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="P14" s="70" t="s">
         <v>26</v>
@@ -3750,7 +3668,7 @@
         <v>281</v>
       </c>
       <c r="R14" s="71" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="S14" s="57"/>
       <c r="T14" s="58"/>
@@ -3768,19 +3686,19 @@
     </row>
     <row r="15" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="C15" s="61" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>15</v>
@@ -3788,14 +3706,14 @@
       <c r="G15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="82" t="s">
-        <v>380</v>
+      <c r="H15" s="94" t="s">
+        <v>403</v>
       </c>
       <c r="I15" s="64" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="J15" s="52" t="s">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="K15" s="56"/>
       <c r="L15" s="46" t="s">
@@ -3805,10 +3723,10 @@
         <v>300</v>
       </c>
       <c r="N15" s="46" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="O15" s="46" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="P15" s="70" t="s">
         <v>26</v>
@@ -3817,7 +3735,7 @@
         <v>281</v>
       </c>
       <c r="R15" s="71" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="S15" s="57"/>
       <c r="T15" s="58"/>
@@ -3835,19 +3753,19 @@
     </row>
     <row r="16" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>15</v>
@@ -3855,27 +3773,27 @@
       <c r="G16" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="81" t="s">
-        <v>393</v>
+      <c r="H16" s="93" t="s">
+        <v>412</v>
       </c>
       <c r="I16" s="64" t="s">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="J16" s="52" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="K16" s="56"/>
       <c r="L16" s="46" t="s">
-        <v>392</v>
+        <v>415</v>
       </c>
       <c r="M16" s="46" t="s">
         <v>291</v>
       </c>
       <c r="N16" s="46" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="O16" s="46" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="P16" s="70" t="s">
         <v>26</v>
@@ -3884,7 +3802,7 @@
         <v>281</v>
       </c>
       <c r="R16" s="71" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="S16" s="57"/>
       <c r="T16" s="58"/>
@@ -3902,19 +3820,19 @@
     </row>
     <row r="17" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="C17" s="61" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>15</v>
@@ -3922,27 +3840,27 @@
       <c r="G17" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="81" t="s">
-        <v>402</v>
+      <c r="H17" s="93" t="s">
+        <v>422</v>
       </c>
       <c r="I17" s="64" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="J17" s="52" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="K17" s="56"/>
       <c r="L17" s="46" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="M17" s="46" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="N17" s="46" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="O17" s="46" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="P17" s="70" t="s">
         <v>26</v>
@@ -3951,7 +3869,7 @@
         <v>281</v>
       </c>
       <c r="R17" s="71" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="S17" s="57"/>
       <c r="T17" s="58"/>
@@ -3969,17 +3887,17 @@
     </row>
     <row r="18" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>15</v>
@@ -3989,21 +3907,21 @@
       </c>
       <c r="H18" s="68"/>
       <c r="I18" s="64" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="J18" s="52" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="K18" s="56"/>
       <c r="L18" s="46" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="M18" s="46" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="N18" s="56"/>
       <c r="O18" s="46" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="P18" s="70" t="s">
         <v>26</v>
@@ -4012,7 +3930,7 @@
         <v>281</v>
       </c>
       <c r="R18" s="71" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="S18" s="57"/>
       <c r="T18" s="58"/>
@@ -4029,24 +3947,56 @@
       <c r="AE18" s="58"/>
     </row>
     <row r="19" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="52"/>
+      <c r="A19" s="41" t="s">
+        <v>341</v>
+      </c>
+      <c r="B19" s="84" t="s">
+        <v>348</v>
+      </c>
+      <c r="C19" s="89" t="s">
+        <v>352</v>
+      </c>
+      <c r="D19" s="90" t="s">
+        <v>268</v>
+      </c>
+      <c r="E19" s="91" t="s">
+        <v>353</v>
+      </c>
+      <c r="F19" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="78" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="68"/>
+      <c r="I19" s="96" t="s">
+        <v>433</v>
+      </c>
+      <c r="J19" s="97" t="s">
+        <v>434</v>
+      </c>
       <c r="K19" s="56"/>
-      <c r="L19" s="56"/>
-      <c r="M19" s="56"/>
-      <c r="N19" s="56"/>
-      <c r="O19" s="46"/>
-      <c r="P19" s="70"/>
-      <c r="Q19" s="72"/>
-      <c r="R19" s="71"/>
+      <c r="L19" s="46" t="s">
+        <v>300</v>
+      </c>
+      <c r="M19" s="46" t="s">
+        <v>301</v>
+      </c>
+      <c r="N19" s="98" t="s">
+        <v>438</v>
+      </c>
+      <c r="O19" s="86" t="s">
+        <v>349</v>
+      </c>
+      <c r="P19" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q19" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="R19" s="71" t="s">
+        <v>17</v>
+      </c>
       <c r="S19" s="57"/>
       <c r="T19" s="58"/>
       <c r="U19" s="58"/>
@@ -4062,24 +4012,56 @@
       <c r="AE19" s="58"/>
     </row>
     <row r="20" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="52"/>
+      <c r="A20" s="41" t="s">
+        <v>342</v>
+      </c>
+      <c r="B20" s="83" t="s">
+        <v>346</v>
+      </c>
+      <c r="C20" s="89" t="s">
+        <v>352</v>
+      </c>
+      <c r="D20" s="90" t="s">
+        <v>268</v>
+      </c>
+      <c r="E20" s="91" t="s">
+        <v>354</v>
+      </c>
+      <c r="F20" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="78" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="68"/>
+      <c r="I20" s="96" t="s">
+        <v>435</v>
+      </c>
+      <c r="J20" s="96" t="s">
+        <v>436</v>
+      </c>
       <c r="K20" s="56"/>
-      <c r="L20" s="56"/>
-      <c r="M20" s="56"/>
-      <c r="N20" s="56"/>
-      <c r="O20" s="46"/>
-      <c r="P20" s="70"/>
-      <c r="Q20" s="72"/>
-      <c r="R20" s="71"/>
+      <c r="L20" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="M20" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="N20" s="98" t="s">
+        <v>439</v>
+      </c>
+      <c r="O20" s="88" t="s">
+        <v>350</v>
+      </c>
+      <c r="P20" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q20" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="R20" s="71" t="s">
+        <v>17</v>
+      </c>
       <c r="S20" s="57"/>
       <c r="T20" s="58"/>
       <c r="U20" s="58"/>
@@ -4095,24 +4077,56 @@
       <c r="AE20" s="58"/>
     </row>
     <row r="21" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="63"/>
+      <c r="A21" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="B21" s="83" t="s">
+        <v>347</v>
+      </c>
+      <c r="C21" s="89" t="s">
+        <v>352</v>
+      </c>
+      <c r="D21" s="90" t="s">
+        <v>268</v>
+      </c>
+      <c r="E21" s="91" t="s">
+        <v>355</v>
+      </c>
+      <c r="F21" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="78" t="s">
+        <v>16</v>
+      </c>
       <c r="H21" s="69"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="52"/>
+      <c r="I21" s="96" t="s">
+        <v>437</v>
+      </c>
+      <c r="J21" s="96" t="s">
+        <v>436</v>
+      </c>
       <c r="K21" s="56"/>
-      <c r="L21" s="56"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="56"/>
-      <c r="O21" s="46"/>
-      <c r="P21" s="70"/>
-      <c r="Q21" s="72"/>
-      <c r="R21" s="71"/>
+      <c r="L21" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="M21" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="N21" s="98" t="s">
+        <v>440</v>
+      </c>
+      <c r="O21" s="87" t="s">
+        <v>351</v>
+      </c>
+      <c r="P21" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="R21" s="71" t="s">
+        <v>17</v>
+      </c>
       <c r="S21" s="57"/>
       <c r="T21" s="58"/>
       <c r="U21" s="58"/>
@@ -4128,24 +4142,56 @@
       <c r="AE21" s="58"/>
     </row>
     <row r="22" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="63"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="52"/>
+      <c r="A22" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="B22" s="83" t="s">
+        <v>358</v>
+      </c>
+      <c r="C22" s="89" t="s">
+        <v>352</v>
+      </c>
+      <c r="D22" s="90" t="s">
+        <v>268</v>
+      </c>
+      <c r="E22" s="91" t="s">
+        <v>356</v>
+      </c>
+      <c r="F22" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="78" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="69"/>
+      <c r="I22" s="96" t="s">
+        <v>437</v>
+      </c>
+      <c r="J22" s="96" t="s">
+        <v>436</v>
+      </c>
       <c r="K22" s="56"/>
-      <c r="L22" s="56"/>
-      <c r="M22" s="56"/>
-      <c r="N22" s="56"/>
-      <c r="O22" s="46"/>
-      <c r="P22" s="70"/>
-      <c r="Q22" s="72"/>
-      <c r="R22" s="71"/>
+      <c r="L22" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="M22" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="N22" s="98" t="s">
+        <v>441</v>
+      </c>
+      <c r="O22" s="87" t="s">
+        <v>351</v>
+      </c>
+      <c r="P22" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q22" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="R22" s="71" t="s">
+        <v>17</v>
+      </c>
       <c r="S22" s="57"/>
       <c r="T22" s="58"/>
       <c r="U22" s="58"/>
@@ -4160,61 +4206,268 @@
       <c r="AD22" s="58"/>
       <c r="AE22" s="58"/>
     </row>
-    <row r="23" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E23" s="59"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="60"/>
-      <c r="O23" s="60"/>
-      <c r="R23" s="60"/>
-      <c r="S23" s="59"/>
-    </row>
-    <row r="24" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E24" s="59"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="60"/>
-      <c r="O24" s="60"/>
-      <c r="R24" s="60"/>
-      <c r="S24" s="59"/>
-    </row>
-    <row r="25" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="60"/>
-      <c r="O25" s="60"/>
-      <c r="R25" s="60"/>
-      <c r="S25" s="59"/>
-    </row>
-    <row r="26" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E26" s="59"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="60"/>
-      <c r="O26" s="60"/>
-      <c r="R26" s="60"/>
-      <c r="S26" s="59"/>
-    </row>
-    <row r="27" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E27" s="59"/>
-      <c r="I27" s="59"/>
-      <c r="J27" s="60"/>
-      <c r="O27" s="60"/>
-      <c r="R27" s="60"/>
-      <c r="S27" s="59"/>
-    </row>
-    <row r="28" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E28" s="59"/>
-      <c r="I28" s="59"/>
-      <c r="J28" s="60"/>
-      <c r="O28" s="60"/>
-      <c r="R28" s="60"/>
-      <c r="S28" s="59"/>
-    </row>
-    <row r="29" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="59"/>
-      <c r="I29" s="59"/>
-      <c r="J29" s="60"/>
-      <c r="O29" s="60"/>
-      <c r="R29" s="60"/>
-      <c r="S29" s="59"/>
+    <row r="23" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="41" t="s">
+        <v>345</v>
+      </c>
+      <c r="B23" s="83" t="s">
+        <v>359</v>
+      </c>
+      <c r="C23" s="89" t="s">
+        <v>352</v>
+      </c>
+      <c r="D23" s="90" t="s">
+        <v>268</v>
+      </c>
+      <c r="E23" s="92" t="s">
+        <v>357</v>
+      </c>
+      <c r="F23" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="78" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="68"/>
+      <c r="I23" s="96" t="s">
+        <v>437</v>
+      </c>
+      <c r="J23" s="96" t="s">
+        <v>436</v>
+      </c>
+      <c r="K23" s="56"/>
+      <c r="L23" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="M23" s="46" t="s">
+        <v>415</v>
+      </c>
+      <c r="N23" s="98" t="s">
+        <v>442</v>
+      </c>
+      <c r="O23" s="87" t="s">
+        <v>351</v>
+      </c>
+      <c r="P23" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q23" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="R23" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="S23" s="57"/>
+      <c r="T23" s="58"/>
+      <c r="U23" s="58"/>
+      <c r="V23" s="58"/>
+      <c r="W23" s="58"/>
+      <c r="X23" s="58"/>
+      <c r="Y23" s="58"/>
+      <c r="Z23" s="58"/>
+      <c r="AA23" s="58"/>
+      <c r="AB23" s="58"/>
+      <c r="AC23" s="58"/>
+      <c r="AD23" s="58"/>
+      <c r="AE23" s="58"/>
+    </row>
+    <row r="24" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="56"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="56"/>
+      <c r="O24" s="46"/>
+      <c r="P24" s="70"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="71"/>
+      <c r="S24" s="57"/>
+      <c r="T24" s="58"/>
+      <c r="U24" s="58"/>
+      <c r="V24" s="58"/>
+      <c r="W24" s="58"/>
+      <c r="X24" s="58"/>
+      <c r="Y24" s="58"/>
+      <c r="Z24" s="58"/>
+      <c r="AA24" s="58"/>
+      <c r="AB24" s="58"/>
+      <c r="AC24" s="58"/>
+      <c r="AD24" s="58"/>
+      <c r="AE24" s="58"/>
+    </row>
+    <row r="25" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="56"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="46"/>
+      <c r="P25" s="70"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="71"/>
+      <c r="S25" s="57"/>
+      <c r="T25" s="58"/>
+      <c r="U25" s="58"/>
+      <c r="V25" s="58"/>
+      <c r="W25" s="58"/>
+      <c r="X25" s="58"/>
+      <c r="Y25" s="58"/>
+      <c r="Z25" s="58"/>
+      <c r="AA25" s="58"/>
+      <c r="AB25" s="58"/>
+      <c r="AC25" s="58"/>
+      <c r="AD25" s="58"/>
+      <c r="AE25" s="58"/>
+    </row>
+    <row r="26" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="56"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="56"/>
+      <c r="N26" s="56"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="70"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="71"/>
+      <c r="S26" s="57"/>
+      <c r="T26" s="58"/>
+      <c r="U26" s="58"/>
+      <c r="V26" s="58"/>
+      <c r="W26" s="58"/>
+      <c r="X26" s="58"/>
+      <c r="Y26" s="58"/>
+      <c r="Z26" s="58"/>
+      <c r="AA26" s="58"/>
+      <c r="AB26" s="58"/>
+      <c r="AC26" s="58"/>
+      <c r="AD26" s="58"/>
+      <c r="AE26" s="58"/>
+    </row>
+    <row r="27" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="64"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="56"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="56"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="46"/>
+      <c r="P27" s="70"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="71"/>
+      <c r="S27" s="57"/>
+      <c r="T27" s="58"/>
+      <c r="U27" s="58"/>
+      <c r="V27" s="58"/>
+      <c r="W27" s="58"/>
+      <c r="X27" s="58"/>
+      <c r="Y27" s="58"/>
+      <c r="Z27" s="58"/>
+      <c r="AA27" s="58"/>
+      <c r="AB27" s="58"/>
+      <c r="AC27" s="58"/>
+      <c r="AD27" s="58"/>
+      <c r="AE27" s="58"/>
+    </row>
+    <row r="28" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="52"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="56"/>
+      <c r="N28" s="56"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="70"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="71"/>
+      <c r="S28" s="57"/>
+      <c r="T28" s="58"/>
+      <c r="U28" s="58"/>
+      <c r="V28" s="58"/>
+      <c r="W28" s="58"/>
+      <c r="X28" s="58"/>
+      <c r="Y28" s="58"/>
+      <c r="Z28" s="58"/>
+      <c r="AA28" s="58"/>
+      <c r="AB28" s="58"/>
+      <c r="AC28" s="58"/>
+      <c r="AD28" s="58"/>
+      <c r="AE28" s="58"/>
+    </row>
+    <row r="29" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="52"/>
+      <c r="K29" s="56"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="56"/>
+      <c r="N29" s="56"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="70"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="71"/>
+      <c r="S29" s="57"/>
+      <c r="T29" s="58"/>
+      <c r="U29" s="58"/>
+      <c r="V29" s="58"/>
+      <c r="W29" s="58"/>
+      <c r="X29" s="58"/>
+      <c r="Y29" s="58"/>
+      <c r="Z29" s="58"/>
+      <c r="AA29" s="58"/>
+      <c r="AB29" s="58"/>
+      <c r="AC29" s="58"/>
+      <c r="AD29" s="58"/>
+      <c r="AE29" s="58"/>
     </row>
     <row r="30" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E30" s="59"/>
@@ -5747,43 +6000,57 @@
     <row r="221" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E221" s="59"/>
       <c r="I221" s="59"/>
-      <c r="J221" s="59"/>
+      <c r="J221" s="60"/>
+      <c r="O221" s="60"/>
+      <c r="R221" s="60"/>
       <c r="S221" s="59"/>
     </row>
     <row r="222" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E222" s="59"/>
       <c r="I222" s="59"/>
-      <c r="J222" s="59"/>
+      <c r="J222" s="60"/>
+      <c r="O222" s="60"/>
+      <c r="R222" s="60"/>
       <c r="S222" s="59"/>
     </row>
     <row r="223" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E223" s="59"/>
       <c r="I223" s="59"/>
-      <c r="J223" s="59"/>
+      <c r="J223" s="60"/>
+      <c r="O223" s="60"/>
+      <c r="R223" s="60"/>
       <c r="S223" s="59"/>
     </row>
     <row r="224" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E224" s="59"/>
       <c r="I224" s="59"/>
-      <c r="J224" s="59"/>
+      <c r="J224" s="60"/>
+      <c r="O224" s="60"/>
+      <c r="R224" s="60"/>
       <c r="S224" s="59"/>
     </row>
     <row r="225" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E225" s="59"/>
       <c r="I225" s="59"/>
-      <c r="J225" s="59"/>
+      <c r="J225" s="60"/>
+      <c r="O225" s="60"/>
+      <c r="R225" s="60"/>
       <c r="S225" s="59"/>
     </row>
     <row r="226" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E226" s="59"/>
       <c r="I226" s="59"/>
-      <c r="J226" s="59"/>
+      <c r="J226" s="60"/>
+      <c r="O226" s="60"/>
+      <c r="R226" s="60"/>
       <c r="S226" s="59"/>
     </row>
     <row r="227" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E227" s="59"/>
       <c r="I227" s="59"/>
-      <c r="J227" s="59"/>
+      <c r="J227" s="60"/>
+      <c r="O227" s="60"/>
+      <c r="R227" s="60"/>
       <c r="S227" s="59"/>
     </row>
     <row r="228" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10424,82 +10691,78 @@
       <c r="J1000" s="59"/>
       <c r="S1000" s="59"/>
     </row>
+    <row r="1001" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E1001" s="59"/>
+      <c r="I1001" s="59"/>
+      <c r="J1001" s="59"/>
+      <c r="S1001" s="59"/>
+    </row>
+    <row r="1002" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E1002" s="59"/>
+      <c r="I1002" s="59"/>
+      <c r="J1002" s="59"/>
+      <c r="S1002" s="59"/>
+    </row>
+    <row r="1003" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E1003" s="59"/>
+      <c r="I1003" s="59"/>
+      <c r="J1003" s="59"/>
+      <c r="S1003" s="59"/>
+    </row>
+    <row r="1004" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E1004" s="59"/>
+      <c r="I1004" s="59"/>
+      <c r="J1004" s="59"/>
+      <c r="S1004" s="59"/>
+    </row>
+    <row r="1005" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E1005" s="59"/>
+      <c r="I1005" s="59"/>
+      <c r="J1005" s="59"/>
+      <c r="S1005" s="59"/>
+    </row>
+    <row r="1006" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E1006" s="59"/>
+      <c r="I1006" s="59"/>
+      <c r="J1006" s="59"/>
+      <c r="S1006" s="59"/>
+    </row>
+    <row r="1007" spans="5:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E1007" s="59"/>
+      <c r="I1007" s="59"/>
+      <c r="J1007" s="59"/>
+      <c r="S1007" s="59"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="22" type="noConversion"/>
-  <conditionalFormatting sqref="Q19:Q22 Q2:Q11">
-    <cfRule type="containsText" dxfId="48" priority="15" operator="containsText" text="New">
+  <conditionalFormatting sqref="Q2:Q29">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="New">
       <formula>NOT(ISERROR(SEARCH("New",Q2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="47" priority="16" operator="containsText" text="New">
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="New">
       <formula>NOT(ISERROR(SEARCH("New",Q2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="17" operator="containsText" text="Closed">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Closed">
       <formula>NOT(ISERROR(SEARCH("Closed",Q2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="45" priority="18" operator="containsText" text="Fix">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Fix">
       <formula>NOT(ISERROR(SEARCH("Fix",Q2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="19" operator="containsText" text="Reopen">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Reopen">
       <formula>NOT(ISERROR(SEARCH("Reopen",Q2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="20" operator="containsText" text="Open">
+    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="Open">
       <formula>NOT(ISERROR(SEARCH("Open",Q2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="21" operator="containsText" text="Reopen">
+    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="Reopen">
       <formula>NOT(ISERROR(SEARCH("Reopen",Q2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q12">
-    <cfRule type="containsText" dxfId="41" priority="8" operator="containsText" text="New">
-      <formula>NOT(ISERROR(SEARCH("New",Q12)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="9" operator="containsText" text="New">
-      <formula>NOT(ISERROR(SEARCH("New",Q12)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="39" priority="10" operator="containsText" text="Closed">
-      <formula>NOT(ISERROR(SEARCH("Closed",Q12)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="11" operator="containsText" text="Fix">
-      <formula>NOT(ISERROR(SEARCH("Fix",Q12)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="12" operator="containsText" text="Reopen">
-      <formula>NOT(ISERROR(SEARCH("Reopen",Q12)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="13" operator="containsText" text="Open">
-      <formula>NOT(ISERROR(SEARCH("Open",Q12)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="35" priority="14" operator="containsText" text="Reopen">
-      <formula>NOT(ISERROR(SEARCH("Reopen",Q12)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q13:Q18">
-    <cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="New">
-      <formula>NOT(ISERROR(SEARCH("New",Q13)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="2" operator="containsText" text="New">
-      <formula>NOT(ISERROR(SEARCH("New",Q13)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="Closed">
-      <formula>NOT(ISERROR(SEARCH("Closed",Q13)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="4" operator="containsText" text="Fix">
-      <formula>NOT(ISERROR(SEARCH("Fix",Q13)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="5" operator="containsText" text="Reopen">
-      <formula>NOT(ISERROR(SEARCH("Reopen",Q13)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="Open">
-      <formula>NOT(ISERROR(SEARCH("Open",Q13)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="7" operator="containsText" text="Reopen">
-      <formula>NOT(ISERROR(SEARCH("Reopen",Q13)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F22">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F29" xr:uid="{872A2AB6-2ADB-4D3A-9A56-79D755130126}">
       <formula1>"valid,invalid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q29" xr:uid="{7A9CF52A-021F-4101-8226-913AE7D0D2C0}">
       <formula1>"New, Open, Fix, Reopen, Closed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10509,7 +10772,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -16033,20 +16296,20 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q2:Q979">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q2:Q979" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"not executed,blocked,failed,passed"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E36" r:id="rId9"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="E8" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="E9" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="E36" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/TestCases_Docs/Bug Report.xlsx
+++ b/TestCases_Docs/Bug Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF3296C-194D-4BBC-8F61-411A3B93FB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85739DBA-C05B-4AE8-8902-B4F8D816AE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="563">
   <si>
     <t>Defect_ID</t>
   </si>
@@ -127,9 +127,6 @@
     <t>Functional</t>
   </si>
   <si>
-    <t>Open</t>
-  </si>
-  <si>
     <t>Mahmoud</t>
   </si>
   <si>
@@ -233,9 +230,6 @@
     <t>Defect_Cart_002</t>
   </si>
   <si>
-    <t>Popup message is displayed "Insufficient stock" when click plus (+) button after reach to Max Stock Quantity</t>
-  </si>
-  <si>
     <t xml:space="preserve">1. Client has a valid account   
 2. Client is logged in   
 3. Product is available in stock with quantity above 1 </t>
@@ -312,9 +306,6 @@
   </si>
   <si>
     <t>Defect_Cart_005</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> out-of-stock product still in cart when Product becomes out of stock before checkout</t>
   </si>
   <si>
     <t>1. Client has a valid account   
@@ -387,9 +378,6 @@
     <t>Defect_Admin_001</t>
   </si>
   <si>
-    <t xml:space="preserve">the product data in the admin's product page dosent contain supplier id </t>
-  </si>
-  <si>
     <t>Open URL, Admin is logged in</t>
   </si>
   <si>
@@ -398,12 +386,6 @@
 3.Enter valid product data
 4.Click Save
 </t>
-  </si>
-  <si>
-    <t>product list is displayed with product name,decription,  image ,price quantity,supplier id for each product</t>
-  </si>
-  <si>
-    <t>supplier id dosent appear</t>
   </si>
   <si>
     <t>TC-Admin-012</t>
@@ -452,9 +434,6 @@
   </si>
   <si>
     <t>Defect_Admin_003</t>
-  </si>
-  <si>
-    <t>admin can't removeproduct without validation</t>
   </si>
   <si>
     <t>Existing product</t>
@@ -2364,12 +2343,65 @@
     <t>1.Error message: "Username is required"
 2.No redirect occurs.</t>
   </si>
+  <si>
+    <t>Unwanted Popup message is displayed "Insufficient stock" when click plus (+) button after reach to Max Stock Quantity</t>
+  </si>
+  <si>
+    <t>out-of-stock product still in cart when Product becomes out of stock before checkout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the product data in the admin's product page dosent contain supplier Email </t>
+  </si>
+  <si>
+    <t>product list is displayed with product name,decription,  image ,price quantity,supplier Email for each product</t>
+  </si>
+  <si>
+    <t>supplier Email dosent appear</t>
+  </si>
+  <si>
+    <t>admin can't remove product without validation</t>
+  </si>
+  <si>
+    <t>Not a Bug</t>
+  </si>
+  <si>
+    <t>Fix</t>
+  </si>
+  <si>
+    <t>Defect_Supplier_001</t>
+  </si>
+  <si>
+    <t>uncorrect validation message when supplier missing required fields on add product page</t>
+  </si>
+  <si>
+    <t>Open URL, Supplier is logged in</t>
+  </si>
+  <si>
+    <t>1.Click on Add Product 
+2.Leave one or more required fields empty 
+3.Click Submit</t>
+  </si>
+  <si>
+    <t>System shows validation message
+"please enter the required data" 
+and product is not submitted</t>
+  </si>
+  <si>
+    <t>System shows "Enter Valid Data"
+ instead of "please enter the required data"</t>
+  </si>
+  <si>
+    <t>SRS-FN-Supplier-001</t>
+  </si>
+  <si>
+    <t>Ganna Adel</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2503,8 +2535,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2531,18 +2569,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF34A853"/>
-        <bgColor rgb="FF34A853"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -2667,19 +2699,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -2724,7 +2743,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2780,11 +2799,11 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2838,17 +2857,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2859,16 +2872,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -2895,7 +2905,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2955,10 +2965,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2973,10 +2980,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2988,7 +2992,7 @@
     <xf numFmtId="0" fontId="23" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3000,11 +3004,30 @@
     <xf numFmtId="0" fontId="23" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3295,8 +3318,8 @@
     <col min="12" max="14" width="16.6640625" customWidth="1"/>
     <col min="15" max="15" width="33.33203125" customWidth="1"/>
     <col min="16" max="18" width="18.21875" customWidth="1"/>
-    <col min="19" max="31" width="18.21875" style="54" customWidth="1"/>
-    <col min="32" max="16384" width="12.6640625" style="54"/>
+    <col min="19" max="31" width="18.21875" style="51" customWidth="1"/>
+    <col min="32" max="16384" width="12.6640625" style="51"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -3354,7 +3377,7 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="53" t="s">
+      <c r="S1" s="50" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="41"/>
@@ -3377,309 +3400,309 @@
       <c r="B2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="E2" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62" t="s">
+      <c r="H2" s="59"/>
+      <c r="I2" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="62" t="s">
+      <c r="J2" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60" t="s">
+      <c r="K2" s="57"/>
+      <c r="L2" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="60" t="s">
+      <c r="M2" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="60" t="s">
+      <c r="O2" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="P2" s="61" t="s">
+      <c r="P2" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q2" s="63" t="s">
+      <c r="Q2" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R2" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="R2" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="S2" s="65"/>
-      <c r="T2" s="55"/>
-      <c r="U2" s="55"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="55"/>
-      <c r="X2" s="55"/>
-      <c r="Y2" s="55"/>
-      <c r="Z2" s="55"/>
-      <c r="AA2" s="55"/>
-      <c r="AB2" s="55"/>
-      <c r="AC2" s="55"/>
-      <c r="AD2" s="55"/>
-      <c r="AE2" s="55"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="52"/>
+      <c r="Z2" s="52"/>
+      <c r="AA2" s="52"/>
+      <c r="AB2" s="52"/>
+      <c r="AC2" s="52"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="52"/>
     </row>
     <row r="3" spans="1:31" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="D3" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="60" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="60" t="s">
+      <c r="F3" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="60" t="s">
+      <c r="G3" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62" t="s">
+      <c r="J3" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="62" t="s">
+      <c r="K3" s="57"/>
+      <c r="L3" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="60" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="60" t="s">
+      <c r="O3" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="60" t="s">
-        <v>43</v>
-      </c>
-      <c r="P3" s="61" t="s">
+      <c r="P3" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q3" s="63" t="s">
+      <c r="Q3" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R3" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="R3" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="S3" s="65"/>
-      <c r="T3" s="55"/>
-      <c r="U3" s="55"/>
-      <c r="V3" s="55"/>
-      <c r="W3" s="55"/>
-      <c r="X3" s="55"/>
-      <c r="Y3" s="55"/>
-      <c r="Z3" s="55"/>
-      <c r="AA3" s="55"/>
-      <c r="AB3" s="55"/>
-      <c r="AC3" s="55"/>
-      <c r="AD3" s="55"/>
-      <c r="AE3" s="55"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="52"/>
+      <c r="U3" s="52"/>
+      <c r="V3" s="52"/>
+      <c r="W3" s="52"/>
+      <c r="X3" s="52"/>
+      <c r="Y3" s="52"/>
+      <c r="Z3" s="52"/>
+      <c r="AA3" s="52"/>
+      <c r="AB3" s="52"/>
+      <c r="AC3" s="52"/>
+      <c r="AD3" s="52"/>
+      <c r="AE3" s="52"/>
     </row>
     <row r="4" spans="1:31" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="D4" s="57"/>
+      <c r="E4" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60" t="s">
+      <c r="F4" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62" t="s">
+      <c r="J4" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="62" t="s">
+      <c r="K4" s="57"/>
+      <c r="L4" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" s="60" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="60" t="s">
+      <c r="O4" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="O4" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="P4" s="61" t="s">
+      <c r="P4" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q4" s="63" t="s">
+      <c r="Q4" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R4" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="R4" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="S4" s="65"/>
-      <c r="T4" s="55"/>
-      <c r="U4" s="55"/>
-      <c r="V4" s="55"/>
-      <c r="W4" s="55"/>
-      <c r="X4" s="55"/>
-      <c r="Y4" s="55"/>
-      <c r="Z4" s="55"/>
-      <c r="AA4" s="55"/>
-      <c r="AB4" s="55"/>
-      <c r="AC4" s="55"/>
-      <c r="AD4" s="55"/>
-      <c r="AE4" s="55"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="52"/>
+      <c r="X4" s="52"/>
+      <c r="Y4" s="52"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="52"/>
+      <c r="AB4" s="52"/>
+      <c r="AC4" s="52"/>
+      <c r="AD4" s="52"/>
+      <c r="AE4" s="52"/>
     </row>
     <row r="5" spans="1:31" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="60" t="s">
+      <c r="D5" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="60" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="60" t="s">
+      <c r="F5" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62" t="s">
+      <c r="J5" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="J5" s="62" t="s">
+      <c r="K5" s="57"/>
+      <c r="L5" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60" t="s">
+      <c r="M5" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="M5" s="60" t="s">
+      <c r="N5" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="N5" s="60" t="s">
+      <c r="O5" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="O5" s="60" t="s">
-        <v>61</v>
-      </c>
-      <c r="P5" s="61" t="s">
+      <c r="P5" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q5" s="63" t="s">
+      <c r="Q5" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R5" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="R5" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="S5" s="65"/>
-      <c r="T5" s="55"/>
-      <c r="U5" s="55"/>
-      <c r="V5" s="55"/>
-      <c r="W5" s="55"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="55"/>
-      <c r="Z5" s="55"/>
-      <c r="AA5" s="55"/>
-      <c r="AB5" s="55"/>
-      <c r="AC5" s="55"/>
-      <c r="AD5" s="55"/>
-      <c r="AE5" s="55"/>
+      <c r="S5" s="62"/>
+      <c r="T5" s="52"/>
+      <c r="U5" s="52"/>
+      <c r="V5" s="52"/>
+      <c r="W5" s="52"/>
+      <c r="X5" s="52"/>
+      <c r="Y5" s="52"/>
+      <c r="Z5" s="52"/>
+      <c r="AA5" s="52"/>
+      <c r="AB5" s="52"/>
+      <c r="AC5" s="52"/>
+      <c r="AD5" s="52"/>
+      <c r="AE5" s="52"/>
     </row>
     <row r="6" spans="1:31" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="C6" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="D6" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="F6" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="60" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="60" t="s">
+      <c r="J6" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62" t="s">
+      <c r="K6" s="59"/>
+      <c r="L6" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="J6" s="62" t="s">
+      <c r="O6" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="K6" s="62"/>
-      <c r="L6" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6" s="62" t="s">
-        <v>68</v>
-      </c>
-      <c r="O6" s="60" t="s">
-        <v>69</v>
-      </c>
-      <c r="P6" s="61" t="s">
+      <c r="P6" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q6" s="63" t="s">
+      <c r="Q6" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R6" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="R6" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="S6" s="66"/>
+      <c r="S6" s="63"/>
       <c r="T6" s="41"/>
       <c r="U6" s="41"/>
       <c r="V6" s="41"/>
@@ -3695,56 +3718,56 @@
     </row>
     <row r="7" spans="1:31" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="D7" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="62" t="s">
+      <c r="F7" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="59"/>
+      <c r="I7" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="60" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="60" t="s">
+      <c r="J7" s="59" t="s">
         <v>73</v>
       </c>
-      <c r="F7" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="62"/>
-      <c r="I7" s="67" t="s">
+      <c r="K7" s="59"/>
+      <c r="L7" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="J7" s="62" t="s">
+      <c r="O7" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="K7" s="62"/>
-      <c r="L7" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7" s="60" t="s">
-        <v>58</v>
-      </c>
-      <c r="N7" s="62" t="s">
-        <v>76</v>
-      </c>
-      <c r="O7" s="60" t="s">
-        <v>77</v>
-      </c>
-      <c r="P7" s="61" t="s">
+      <c r="P7" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q7" s="63" t="s">
+      <c r="Q7" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R7" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="R7" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="S7" s="66"/>
+      <c r="S7" s="63"/>
       <c r="T7" s="41"/>
       <c r="U7" s="41"/>
       <c r="V7" s="41"/>
@@ -3760,121 +3783,121 @@
     </row>
     <row r="8" spans="1:31" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="D8" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="62" t="s">
+      <c r="F8" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="59"/>
+      <c r="I8" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="60" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="62" t="s">
+      <c r="J8" s="59" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="66"/>
+      <c r="L8" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="62"/>
-      <c r="I8" s="68" t="s">
+      <c r="O8" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="J8" s="62" t="s">
-        <v>79</v>
-      </c>
-      <c r="K8" s="69"/>
-      <c r="L8" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8" s="60" t="s">
-        <v>58</v>
-      </c>
-      <c r="N8" s="62" t="s">
-        <v>83</v>
-      </c>
-      <c r="O8" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="P8" s="61" t="s">
+      <c r="P8" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q8" s="63" t="s">
+      <c r="Q8" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R8" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="R8" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="S8" s="70"/>
-      <c r="T8" s="56"/>
-      <c r="U8" s="56"/>
-      <c r="V8" s="56"/>
-      <c r="W8" s="56"/>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="56"/>
-      <c r="Z8" s="56"/>
-      <c r="AA8" s="56"/>
-      <c r="AB8" s="56"/>
-      <c r="AC8" s="56"/>
-      <c r="AD8" s="56"/>
-      <c r="AE8" s="56"/>
+      <c r="S8" s="67"/>
+      <c r="T8" s="53"/>
+      <c r="U8" s="53"/>
+      <c r="V8" s="53"/>
+      <c r="W8" s="53"/>
+      <c r="X8" s="53"/>
+      <c r="Y8" s="53"/>
+      <c r="Z8" s="53"/>
+      <c r="AA8" s="53"/>
+      <c r="AB8" s="53"/>
+      <c r="AC8" s="53"/>
+      <c r="AD8" s="53"/>
+      <c r="AE8" s="53"/>
     </row>
     <row r="9" spans="1:31" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="C9" s="59" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="E9" s="59" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="62" t="s">
+      <c r="F9" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="69" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="59"/>
+      <c r="I9" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="J9" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="E9" s="62" t="s">
+      <c r="K9" s="59"/>
+      <c r="L9" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="F9" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="72" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="62"/>
-      <c r="I9" s="68" t="s">
+      <c r="O9" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="J9" s="60" t="s">
-        <v>91</v>
-      </c>
-      <c r="K9" s="62"/>
-      <c r="L9" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="M9" s="60" t="s">
-        <v>59</v>
-      </c>
-      <c r="N9" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="O9" s="60" t="s">
-        <v>93</v>
-      </c>
-      <c r="P9" s="61" t="s">
+      <c r="P9" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q9" s="63" t="s">
+      <c r="Q9" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R9" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="R9" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="S9" s="66"/>
+      <c r="S9" s="63"/>
       <c r="T9" s="41"/>
       <c r="U9" s="41"/>
       <c r="V9" s="41"/>
@@ -3890,1390 +3913,1390 @@
     </row>
     <row r="10" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="70" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="F10" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="57"/>
+      <c r="I10" s="65" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="62" t="s">
+      <c r="J10" s="59" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="73" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" s="74" t="s">
+      <c r="K10" s="57"/>
+      <c r="L10" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="F10" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="75" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="60"/>
-      <c r="I10" s="68" t="s">
-        <v>98</v>
-      </c>
-      <c r="J10" s="62" t="s">
-        <v>99</v>
-      </c>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="M10" s="60" t="s">
-        <v>59</v>
-      </c>
-      <c r="N10" s="62" t="s">
-        <v>100</v>
-      </c>
-      <c r="O10" s="60" t="s">
-        <v>93</v>
-      </c>
-      <c r="P10" s="61" t="s">
+      <c r="O10" s="57" t="s">
+        <v>90</v>
+      </c>
+      <c r="P10" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q10" s="63" t="s">
+      <c r="Q10" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R10" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="R10" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="S10" s="65"/>
-      <c r="T10" s="57"/>
-      <c r="U10" s="57"/>
-      <c r="V10" s="57"/>
-      <c r="W10" s="57"/>
-      <c r="X10" s="57"/>
-      <c r="Y10" s="57"/>
-      <c r="Z10" s="57"/>
-      <c r="AA10" s="57"/>
-      <c r="AB10" s="57"/>
-      <c r="AC10" s="57"/>
-      <c r="AD10" s="57"/>
-      <c r="AE10" s="57"/>
+      <c r="S10" s="62"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="54"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="54"/>
+      <c r="X10" s="54"/>
+      <c r="Y10" s="54"/>
+      <c r="Z10" s="54"/>
+      <c r="AA10" s="54"/>
+      <c r="AB10" s="54"/>
+      <c r="AC10" s="54"/>
+      <c r="AD10" s="54"/>
+      <c r="AE10" s="54"/>
     </row>
     <row r="11" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="C11" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="57"/>
+      <c r="I11" s="64" t="s">
+        <v>550</v>
+      </c>
+      <c r="J11" s="59" t="s">
+        <v>551</v>
+      </c>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="O11" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="60" t="s">
+      <c r="P11" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q11" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R11" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="F11" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="75" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="60"/>
-      <c r="I11" s="67" t="s">
-        <v>105</v>
-      </c>
-      <c r="J11" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="K11" s="60"/>
-      <c r="L11" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="M11" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="N11" s="60" t="s">
-        <v>107</v>
-      </c>
-      <c r="O11" s="60" t="s">
-        <v>108</v>
-      </c>
-      <c r="P11" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q11" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R11" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="S11" s="65"/>
-      <c r="T11" s="57"/>
-      <c r="U11" s="57"/>
-      <c r="V11" s="57"/>
-      <c r="W11" s="57"/>
-      <c r="X11" s="57"/>
-      <c r="Y11" s="57"/>
-      <c r="Z11" s="57"/>
-      <c r="AA11" s="57"/>
-      <c r="AB11" s="57"/>
-      <c r="AC11" s="57"/>
-      <c r="AD11" s="57"/>
-      <c r="AE11" s="57"/>
+      <c r="S11" s="62"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="54"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="54"/>
+      <c r="X11" s="54"/>
+      <c r="Y11" s="54"/>
+      <c r="Z11" s="54"/>
+      <c r="AA11" s="54"/>
+      <c r="AB11" s="54"/>
+      <c r="AC11" s="54"/>
+      <c r="AD11" s="54"/>
+      <c r="AE11" s="54"/>
     </row>
     <row r="12" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>108</v>
+      </c>
+      <c r="I12" s="64" t="s">
+        <v>109</v>
+      </c>
+      <c r="J12" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="K12" s="57"/>
+      <c r="L12" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="N12" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="O12" s="57" t="s">
+        <v>102</v>
+      </c>
+      <c r="P12" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q12" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R12" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="60" t="s">
-        <v>112</v>
-      </c>
-      <c r="E12" s="60" t="s">
-        <v>113</v>
-      </c>
-      <c r="F12" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="75" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="60" t="s">
-        <v>114</v>
-      </c>
-      <c r="I12" s="67" t="s">
-        <v>115</v>
-      </c>
-      <c r="J12" s="62" t="s">
-        <v>116</v>
-      </c>
-      <c r="K12" s="60"/>
-      <c r="L12" s="60" t="s">
-        <v>58</v>
-      </c>
-      <c r="M12" s="60" t="s">
-        <v>117</v>
-      </c>
-      <c r="N12" s="60" t="s">
-        <v>118</v>
-      </c>
-      <c r="O12" s="60" t="s">
-        <v>108</v>
-      </c>
-      <c r="P12" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q12" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R12" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="S12" s="65"/>
-      <c r="T12" s="57"/>
-      <c r="U12" s="57"/>
-      <c r="V12" s="57"/>
-      <c r="W12" s="57"/>
-      <c r="X12" s="57"/>
-      <c r="Y12" s="57"/>
-      <c r="Z12" s="57"/>
-      <c r="AA12" s="57"/>
-      <c r="AB12" s="57"/>
-      <c r="AC12" s="57"/>
-      <c r="AD12" s="57"/>
-      <c r="AE12" s="57"/>
+      <c r="S12" s="62"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="54"/>
+      <c r="V12" s="54"/>
+      <c r="W12" s="54"/>
+      <c r="X12" s="54"/>
+      <c r="Y12" s="54"/>
+      <c r="Z12" s="54"/>
+      <c r="AA12" s="54"/>
+      <c r="AB12" s="54"/>
+      <c r="AC12" s="54"/>
+      <c r="AD12" s="54"/>
+      <c r="AE12" s="54"/>
     </row>
     <row r="13" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="C13" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="57" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" s="57" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="I13" s="64" t="s">
+        <v>117</v>
+      </c>
+      <c r="J13" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57" t="s">
         <v>119</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="M13" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="N13" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="C13" s="60" t="s">
+      <c r="O13" s="57" t="s">
+        <v>121</v>
+      </c>
+      <c r="P13" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q13" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R13" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="60" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" s="60" t="s">
-        <v>122</v>
-      </c>
-      <c r="F13" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="60" t="s">
-        <v>123</v>
-      </c>
-      <c r="I13" s="67" t="s">
-        <v>124</v>
-      </c>
-      <c r="J13" s="62" t="s">
-        <v>125</v>
-      </c>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="M13" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="N13" s="60" t="s">
-        <v>127</v>
-      </c>
-      <c r="O13" s="60" t="s">
-        <v>128</v>
-      </c>
-      <c r="P13" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q13" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R13" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="S13" s="65"/>
-      <c r="T13" s="57"/>
-      <c r="U13" s="57"/>
-      <c r="V13" s="57"/>
-      <c r="W13" s="57"/>
-      <c r="X13" s="57"/>
-      <c r="Y13" s="57"/>
-      <c r="Z13" s="57"/>
-      <c r="AA13" s="57"/>
-      <c r="AB13" s="57"/>
-      <c r="AC13" s="57"/>
-      <c r="AD13" s="57"/>
-      <c r="AE13" s="57"/>
+      <c r="S13" s="62"/>
+      <c r="T13" s="54"/>
+      <c r="U13" s="54"/>
+      <c r="V13" s="54"/>
+      <c r="W13" s="54"/>
+      <c r="X13" s="54"/>
+      <c r="Y13" s="54"/>
+      <c r="Z13" s="54"/>
+      <c r="AA13" s="54"/>
+      <c r="AB13" s="54"/>
+      <c r="AC13" s="54"/>
+      <c r="AD13" s="54"/>
+      <c r="AE13" s="54"/>
     </row>
     <row r="14" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="I14" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="J14" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="K14" s="57"/>
+      <c r="L14" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M14" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="O14" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="D14" s="60" t="s">
-        <v>132</v>
-      </c>
-      <c r="E14" s="60" t="s">
-        <v>133</v>
-      </c>
-      <c r="F14" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="G14" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="I14" s="67" t="s">
-        <v>135</v>
-      </c>
-      <c r="J14" s="62" t="s">
-        <v>136</v>
-      </c>
-      <c r="K14" s="60"/>
-      <c r="L14" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="M14" s="60" t="s">
-        <v>58</v>
-      </c>
-      <c r="N14" s="60" t="s">
-        <v>137</v>
-      </c>
-      <c r="O14" s="60" t="s">
-        <v>138</v>
-      </c>
-      <c r="P14" s="61" t="s">
+      <c r="P14" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q14" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R14" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="S14" s="65"/>
-      <c r="T14" s="57"/>
-      <c r="U14" s="57"/>
-      <c r="V14" s="57"/>
-      <c r="W14" s="57"/>
-      <c r="X14" s="57"/>
-      <c r="Y14" s="57"/>
-      <c r="Z14" s="57"/>
-      <c r="AA14" s="57"/>
-      <c r="AB14" s="57"/>
-      <c r="AC14" s="57"/>
-      <c r="AD14" s="57"/>
-      <c r="AE14" s="57"/>
+      <c r="Q14" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R14" s="61" t="s">
+        <v>103</v>
+      </c>
+      <c r="S14" s="62"/>
+      <c r="T14" s="54"/>
+      <c r="U14" s="54"/>
+      <c r="V14" s="54"/>
+      <c r="W14" s="54"/>
+      <c r="X14" s="54"/>
+      <c r="Y14" s="54"/>
+      <c r="Z14" s="54"/>
+      <c r="AA14" s="54"/>
+      <c r="AB14" s="54"/>
+      <c r="AC14" s="54"/>
+      <c r="AD14" s="54"/>
+      <c r="AE14" s="54"/>
     </row>
     <row r="15" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="57" t="s">
+        <v>134</v>
+      </c>
+      <c r="D15" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="E15" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="F15" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="I15" s="64" t="s">
+        <v>138</v>
+      </c>
+      <c r="J15" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="K15" s="57"/>
+      <c r="L15" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M15" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="N15" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="C15" s="60" t="s">
+      <c r="O15" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="D15" s="60" t="s">
-        <v>142</v>
-      </c>
-      <c r="E15" s="60" t="s">
-        <v>143</v>
-      </c>
-      <c r="F15" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" s="60" t="s">
-        <v>144</v>
-      </c>
-      <c r="I15" s="67" t="s">
-        <v>145</v>
-      </c>
-      <c r="J15" s="62" t="s">
-        <v>146</v>
-      </c>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="M15" s="60" t="s">
-        <v>58</v>
-      </c>
-      <c r="N15" s="60" t="s">
-        <v>147</v>
-      </c>
-      <c r="O15" s="60" t="s">
-        <v>148</v>
-      </c>
-      <c r="P15" s="61" t="s">
+      <c r="P15" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q15" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R15" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="S15" s="65"/>
-      <c r="T15" s="57"/>
-      <c r="U15" s="57"/>
-      <c r="V15" s="57"/>
-      <c r="W15" s="57"/>
-      <c r="X15" s="57"/>
-      <c r="Y15" s="57"/>
-      <c r="Z15" s="57"/>
-      <c r="AA15" s="57"/>
-      <c r="AB15" s="57"/>
-      <c r="AC15" s="57"/>
-      <c r="AD15" s="57"/>
-      <c r="AE15" s="57"/>
+      <c r="Q15" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R15" s="61" t="s">
+        <v>103</v>
+      </c>
+      <c r="S15" s="62"/>
+      <c r="T15" s="54"/>
+      <c r="U15" s="54"/>
+      <c r="V15" s="54"/>
+      <c r="W15" s="54"/>
+      <c r="X15" s="54"/>
+      <c r="Y15" s="54"/>
+      <c r="Z15" s="54"/>
+      <c r="AA15" s="54"/>
+      <c r="AB15" s="54"/>
+      <c r="AC15" s="54"/>
+      <c r="AD15" s="54"/>
+      <c r="AE15" s="54"/>
     </row>
     <row r="16" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="57" t="s">
+        <v>144</v>
+      </c>
+      <c r="E16" s="57" t="s">
+        <v>145</v>
+      </c>
+      <c r="F16" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="57" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" s="64" t="s">
+        <v>147</v>
+      </c>
+      <c r="J16" s="59" t="s">
+        <v>148</v>
+      </c>
+      <c r="K16" s="57"/>
+      <c r="L16" s="57" t="s">
         <v>149</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="M16" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="N16" s="57" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="O16" s="57" t="s">
+        <v>151</v>
+      </c>
+      <c r="P16" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q16" s="60" t="s">
+        <v>553</v>
+      </c>
+      <c r="R16" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="D16" s="60" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="F16" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="60" t="s">
-        <v>153</v>
-      </c>
-      <c r="I16" s="67" t="s">
-        <v>154</v>
-      </c>
-      <c r="J16" s="62" t="s">
-        <v>155</v>
-      </c>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="M16" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="N16" s="60" t="s">
-        <v>157</v>
-      </c>
-      <c r="O16" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="P16" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q16" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R16" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="S16" s="65"/>
-      <c r="T16" s="57"/>
-      <c r="U16" s="57"/>
-      <c r="V16" s="57"/>
-      <c r="W16" s="57"/>
-      <c r="X16" s="57"/>
-      <c r="Y16" s="57"/>
-      <c r="Z16" s="57"/>
-      <c r="AA16" s="57"/>
-      <c r="AB16" s="57"/>
-      <c r="AC16" s="57"/>
-      <c r="AD16" s="57"/>
-      <c r="AE16" s="57"/>
+      <c r="S16" s="62"/>
+      <c r="T16" s="54"/>
+      <c r="U16" s="54"/>
+      <c r="V16" s="54"/>
+      <c r="W16" s="54"/>
+      <c r="X16" s="54"/>
+      <c r="Y16" s="54"/>
+      <c r="Z16" s="54"/>
+      <c r="AA16" s="54"/>
+      <c r="AB16" s="54"/>
+      <c r="AC16" s="54"/>
+      <c r="AD16" s="54"/>
+      <c r="AE16" s="54"/>
     </row>
     <row r="17" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="57" t="s">
+        <v>154</v>
+      </c>
+      <c r="E17" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="F17" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="57" t="s">
+        <v>156</v>
+      </c>
+      <c r="I17" s="64" t="s">
+        <v>157</v>
+      </c>
+      <c r="J17" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="K17" s="57"/>
+      <c r="L17" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="M17" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="N17" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="O17" s="57" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="60" t="s">
+      <c r="P17" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q17" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R17" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="D17" s="60" t="s">
-        <v>161</v>
-      </c>
-      <c r="E17" s="60" t="s">
-        <v>162</v>
-      </c>
-      <c r="F17" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="60" t="s">
-        <v>163</v>
-      </c>
-      <c r="I17" s="67" t="s">
-        <v>164</v>
-      </c>
-      <c r="J17" s="62" t="s">
-        <v>165</v>
-      </c>
-      <c r="K17" s="60"/>
-      <c r="L17" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="M17" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="N17" s="60" t="s">
-        <v>166</v>
-      </c>
-      <c r="O17" s="60" t="s">
-        <v>167</v>
-      </c>
-      <c r="P17" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q17" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R17" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="S17" s="65"/>
-      <c r="T17" s="57"/>
-      <c r="U17" s="57"/>
-      <c r="V17" s="57"/>
-      <c r="W17" s="57"/>
-      <c r="X17" s="57"/>
-      <c r="Y17" s="57"/>
-      <c r="Z17" s="57"/>
-      <c r="AA17" s="57"/>
-      <c r="AB17" s="57"/>
-      <c r="AC17" s="57"/>
-      <c r="AD17" s="57"/>
-      <c r="AE17" s="57"/>
+      <c r="S17" s="62"/>
+      <c r="T17" s="54"/>
+      <c r="U17" s="54"/>
+      <c r="V17" s="54"/>
+      <c r="W17" s="54"/>
+      <c r="X17" s="54"/>
+      <c r="Y17" s="54"/>
+      <c r="Z17" s="54"/>
+      <c r="AA17" s="54"/>
+      <c r="AB17" s="54"/>
+      <c r="AC17" s="54"/>
+      <c r="AD17" s="54"/>
+      <c r="AE17" s="54"/>
     </row>
     <row r="18" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C18" s="60" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57" t="s">
+        <v>163</v>
+      </c>
+      <c r="F18" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="57"/>
+      <c r="I18" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="J18" s="59" t="s">
+        <v>165</v>
+      </c>
+      <c r="K18" s="57"/>
+      <c r="L18" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="M18" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="N18" s="57"/>
+      <c r="O18" s="57" t="s">
+        <v>166</v>
+      </c>
+      <c r="P18" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q18" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R18" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60" t="s">
-        <v>170</v>
-      </c>
-      <c r="F18" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="60"/>
-      <c r="I18" s="67" t="s">
-        <v>171</v>
-      </c>
-      <c r="J18" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="K18" s="60"/>
-      <c r="L18" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="M18" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="N18" s="60"/>
-      <c r="O18" s="60" t="s">
-        <v>173</v>
-      </c>
-      <c r="P18" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q18" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R18" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="S18" s="65"/>
-      <c r="T18" s="57"/>
-      <c r="U18" s="57"/>
-      <c r="V18" s="57"/>
-      <c r="W18" s="57"/>
-      <c r="X18" s="57"/>
-      <c r="Y18" s="57"/>
-      <c r="Z18" s="57"/>
-      <c r="AA18" s="57"/>
-      <c r="AB18" s="57"/>
-      <c r="AC18" s="57"/>
-      <c r="AD18" s="57"/>
-      <c r="AE18" s="57"/>
+      <c r="S18" s="62"/>
+      <c r="T18" s="54"/>
+      <c r="U18" s="54"/>
+      <c r="V18" s="54"/>
+      <c r="W18" s="54"/>
+      <c r="X18" s="54"/>
+      <c r="Y18" s="54"/>
+      <c r="Z18" s="54"/>
+      <c r="AA18" s="54"/>
+      <c r="AB18" s="54"/>
+      <c r="AC18" s="54"/>
+      <c r="AD18" s="54"/>
+      <c r="AE18" s="54"/>
     </row>
     <row r="19" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C19" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="D19" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="57" t="s">
+        <v>170</v>
+      </c>
+      <c r="F19" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57" t="s">
+        <v>171</v>
+      </c>
+      <c r="J19" s="59" t="s">
+        <v>172</v>
+      </c>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="M19" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="N19" s="57" t="s">
+        <v>173</v>
+      </c>
+      <c r="O19" s="57" t="s">
         <v>174</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C19" s="60" t="s">
-        <v>176</v>
-      </c>
-      <c r="D19" s="60" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="60" t="s">
-        <v>177</v>
-      </c>
-      <c r="F19" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="G19" s="75" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60" t="s">
-        <v>178</v>
-      </c>
-      <c r="J19" s="62" t="s">
-        <v>179</v>
-      </c>
-      <c r="K19" s="60"/>
-      <c r="L19" s="60" t="s">
-        <v>58</v>
-      </c>
-      <c r="M19" s="60" t="s">
-        <v>59</v>
-      </c>
-      <c r="N19" s="60" t="s">
-        <v>180</v>
-      </c>
-      <c r="O19" s="60" t="s">
-        <v>181</v>
-      </c>
-      <c r="P19" s="61" t="s">
+      <c r="P19" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q19" s="63" t="s">
+      <c r="Q19" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R19" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="R19" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="S19" s="65"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="57"/>
-      <c r="Y19" s="57"/>
-      <c r="Z19" s="57"/>
-      <c r="AA19" s="57"/>
-      <c r="AB19" s="57"/>
-      <c r="AC19" s="57"/>
-      <c r="AD19" s="57"/>
-      <c r="AE19" s="57"/>
+      <c r="S19" s="62"/>
+      <c r="T19" s="54"/>
+      <c r="U19" s="54"/>
+      <c r="V19" s="54"/>
+      <c r="W19" s="54"/>
+      <c r="X19" s="54"/>
+      <c r="Y19" s="54"/>
+      <c r="Z19" s="54"/>
+      <c r="AA19" s="54"/>
+      <c r="AB19" s="54"/>
+      <c r="AC19" s="54"/>
+      <c r="AD19" s="54"/>
+      <c r="AE19" s="54"/>
     </row>
     <row r="20" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C20" s="60" t="s">
         <v>176</v>
       </c>
-      <c r="D20" s="60" t="s">
+      <c r="C20" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="D20" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="60" t="s">
-        <v>184</v>
-      </c>
-      <c r="F20" s="60" t="s">
+      <c r="E20" s="57" t="s">
+        <v>177</v>
+      </c>
+      <c r="F20" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="G20" s="75" t="s">
+      <c r="G20" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60" t="s">
-        <v>185</v>
-      </c>
-      <c r="J20" s="60" t="s">
-        <v>186</v>
-      </c>
-      <c r="K20" s="60"/>
-      <c r="L20" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="M20" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="N20" s="60" t="s">
-        <v>187</v>
-      </c>
-      <c r="O20" s="60" t="s">
-        <v>188</v>
-      </c>
-      <c r="P20" s="61" t="s">
+      <c r="H20" s="57"/>
+      <c r="I20" s="57" t="s">
+        <v>178</v>
+      </c>
+      <c r="J20" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="M20" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="N20" s="57" t="s">
+        <v>180</v>
+      </c>
+      <c r="O20" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="P20" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q20" s="63" t="s">
+      <c r="Q20" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R20" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="R20" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="S20" s="65"/>
-      <c r="T20" s="57"/>
-      <c r="U20" s="57"/>
-      <c r="V20" s="57"/>
-      <c r="W20" s="57"/>
-      <c r="X20" s="57"/>
-      <c r="Y20" s="57"/>
-      <c r="Z20" s="57"/>
-      <c r="AA20" s="57"/>
-      <c r="AB20" s="57"/>
-      <c r="AC20" s="57"/>
-      <c r="AD20" s="57"/>
-      <c r="AE20" s="57"/>
+      <c r="S20" s="62"/>
+      <c r="T20" s="54"/>
+      <c r="U20" s="54"/>
+      <c r="V20" s="54"/>
+      <c r="W20" s="54"/>
+      <c r="X20" s="54"/>
+      <c r="Y20" s="54"/>
+      <c r="Z20" s="54"/>
+      <c r="AA20" s="54"/>
+      <c r="AB20" s="54"/>
+      <c r="AC20" s="54"/>
+      <c r="AD20" s="54"/>
+      <c r="AE20" s="54"/>
     </row>
     <row r="21" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C21" s="60" t="s">
-        <v>176</v>
-      </c>
-      <c r="D21" s="60" t="s">
+        <v>183</v>
+      </c>
+      <c r="C21" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="D21" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="60" t="s">
-        <v>191</v>
-      </c>
-      <c r="F21" s="60" t="s">
+      <c r="E21" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="F21" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="G21" s="75" t="s">
+      <c r="G21" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="60"/>
-      <c r="I21" s="60" t="s">
-        <v>192</v>
-      </c>
-      <c r="J21" s="60" t="s">
+      <c r="H21" s="57"/>
+      <c r="I21" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="J21" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="M21" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="N21" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="K21" s="60"/>
-      <c r="L21" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="M21" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="N21" s="60" t="s">
-        <v>193</v>
-      </c>
-      <c r="O21" s="60" t="s">
-        <v>194</v>
-      </c>
-      <c r="P21" s="61" t="s">
+      <c r="O21" s="57" t="s">
+        <v>187</v>
+      </c>
+      <c r="P21" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q21" s="63" t="s">
+      <c r="Q21" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R21" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="R21" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="S21" s="65"/>
-      <c r="T21" s="57"/>
-      <c r="U21" s="57"/>
-      <c r="V21" s="57"/>
-      <c r="W21" s="57"/>
-      <c r="X21" s="57"/>
-      <c r="Y21" s="57"/>
-      <c r="Z21" s="57"/>
-      <c r="AA21" s="57"/>
-      <c r="AB21" s="57"/>
-      <c r="AC21" s="57"/>
-      <c r="AD21" s="57"/>
-      <c r="AE21" s="57"/>
+      <c r="S21" s="62"/>
+      <c r="T21" s="54"/>
+      <c r="U21" s="54"/>
+      <c r="V21" s="54"/>
+      <c r="W21" s="54"/>
+      <c r="X21" s="54"/>
+      <c r="Y21" s="54"/>
+      <c r="Z21" s="54"/>
+      <c r="AA21" s="54"/>
+      <c r="AB21" s="54"/>
+      <c r="AC21" s="54"/>
+      <c r="AD21" s="54"/>
+      <c r="AE21" s="54"/>
     </row>
     <row r="22" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C22" s="60" t="s">
-        <v>176</v>
-      </c>
-      <c r="D22" s="60" t="s">
+        <v>189</v>
+      </c>
+      <c r="C22" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="D22" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="60" t="s">
-        <v>197</v>
-      </c>
-      <c r="F22" s="60" t="s">
+      <c r="E22" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="F22" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="G22" s="75" t="s">
+      <c r="G22" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60" t="s">
-        <v>192</v>
-      </c>
-      <c r="J22" s="60" t="s">
-        <v>186</v>
-      </c>
-      <c r="K22" s="60"/>
-      <c r="L22" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="M22" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="N22" s="60" t="s">
-        <v>198</v>
-      </c>
-      <c r="O22" s="60" t="s">
-        <v>194</v>
-      </c>
-      <c r="P22" s="61" t="s">
+      <c r="H22" s="57"/>
+      <c r="I22" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="J22" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="M22" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="N22" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="O22" s="57" t="s">
+        <v>187</v>
+      </c>
+      <c r="P22" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q22" s="63" t="s">
+      <c r="Q22" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R22" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="R22" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="S22" s="65"/>
-      <c r="T22" s="57"/>
-      <c r="U22" s="57"/>
-      <c r="V22" s="57"/>
-      <c r="W22" s="57"/>
-      <c r="X22" s="57"/>
-      <c r="Y22" s="57"/>
-      <c r="Z22" s="57"/>
-      <c r="AA22" s="57"/>
-      <c r="AB22" s="57"/>
-      <c r="AC22" s="57"/>
-      <c r="AD22" s="57"/>
-      <c r="AE22" s="57"/>
+      <c r="S22" s="62"/>
+      <c r="T22" s="54"/>
+      <c r="U22" s="54"/>
+      <c r="V22" s="54"/>
+      <c r="W22" s="54"/>
+      <c r="X22" s="54"/>
+      <c r="Y22" s="54"/>
+      <c r="Z22" s="54"/>
+      <c r="AA22" s="54"/>
+      <c r="AB22" s="54"/>
+      <c r="AC22" s="54"/>
+      <c r="AD22" s="54"/>
+      <c r="AE22" s="54"/>
     </row>
     <row r="23" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C23" s="60" t="s">
-        <v>176</v>
-      </c>
-      <c r="D23" s="60" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="D23" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="76" t="s">
-        <v>201</v>
-      </c>
-      <c r="F23" s="60" t="s">
+      <c r="E23" s="73" t="s">
+        <v>194</v>
+      </c>
+      <c r="F23" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="G23" s="75" t="s">
+      <c r="G23" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="H23" s="60"/>
-      <c r="I23" s="60" t="s">
-        <v>192</v>
-      </c>
-      <c r="J23" s="60" t="s">
-        <v>186</v>
-      </c>
-      <c r="K23" s="60"/>
-      <c r="L23" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="M23" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="N23" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="O23" s="60" t="s">
-        <v>194</v>
-      </c>
-      <c r="P23" s="61" t="s">
+      <c r="H23" s="57"/>
+      <c r="I23" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="J23" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="M23" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="N23" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="O23" s="57" t="s">
+        <v>187</v>
+      </c>
+      <c r="P23" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q23" s="63" t="s">
+      <c r="Q23" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R23" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="R23" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="S23" s="65"/>
-      <c r="T23" s="57"/>
-      <c r="U23" s="57"/>
-      <c r="V23" s="57"/>
-      <c r="W23" s="57"/>
-      <c r="X23" s="57"/>
-      <c r="Y23" s="57"/>
-      <c r="Z23" s="57"/>
-      <c r="AA23" s="57"/>
-      <c r="AB23" s="57"/>
-      <c r="AC23" s="57"/>
-      <c r="AD23" s="57"/>
-      <c r="AE23" s="57"/>
+      <c r="S23" s="62"/>
+      <c r="T23" s="54"/>
+      <c r="U23" s="54"/>
+      <c r="V23" s="54"/>
+      <c r="W23" s="54"/>
+      <c r="X23" s="54"/>
+      <c r="Y23" s="54"/>
+      <c r="Z23" s="54"/>
+      <c r="AA23" s="54"/>
+      <c r="AB23" s="54"/>
+      <c r="AC23" s="54"/>
+      <c r="AD23" s="54"/>
+      <c r="AE23" s="54"/>
     </row>
     <row r="24" spans="1:31" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24" s="94" t="s">
+        <v>197</v>
+      </c>
+      <c r="C24" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="D24" s="57" t="s">
+        <v>199</v>
+      </c>
+      <c r="E24" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="F24" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="I24" s="64" t="s">
+        <v>202</v>
+      </c>
+      <c r="J24" s="59" t="s">
         <v>203</v>
       </c>
-      <c r="B24" s="50" t="s">
+      <c r="K24" s="74" t="s">
         <v>204</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="L24" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="N24" s="57" t="s">
         <v>205</v>
       </c>
-      <c r="D24" s="60" t="s">
+      <c r="O24" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="E24" s="60" t="s">
+      <c r="P24" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q24" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R24" s="61" t="s">
         <v>207</v>
       </c>
-      <c r="F24" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H24" s="60" t="s">
-        <v>208</v>
-      </c>
-      <c r="I24" s="67" t="s">
-        <v>209</v>
-      </c>
-      <c r="J24" s="62" t="s">
-        <v>210</v>
-      </c>
-      <c r="K24" s="77" t="s">
-        <v>211</v>
-      </c>
-      <c r="L24" s="60" t="s">
-        <v>58</v>
-      </c>
-      <c r="M24" s="60" t="s">
-        <v>59</v>
-      </c>
-      <c r="N24" s="60" t="s">
-        <v>212</v>
-      </c>
-      <c r="O24" s="60" t="s">
-        <v>213</v>
-      </c>
-      <c r="P24" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q24" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R24" s="64" t="s">
-        <v>214</v>
-      </c>
-      <c r="S24" s="65"/>
-      <c r="T24" s="57"/>
-      <c r="U24" s="57"/>
-      <c r="V24" s="57"/>
-      <c r="W24" s="57"/>
-      <c r="X24" s="57"/>
-      <c r="Y24" s="57"/>
-      <c r="Z24" s="57"/>
-      <c r="AA24" s="57"/>
-      <c r="AB24" s="57"/>
-      <c r="AC24" s="57"/>
-      <c r="AD24" s="57"/>
-      <c r="AE24" s="57"/>
+      <c r="S24" s="62"/>
+      <c r="T24" s="54"/>
+      <c r="U24" s="54"/>
+      <c r="V24" s="54"/>
+      <c r="W24" s="54"/>
+      <c r="X24" s="54"/>
+      <c r="Y24" s="54"/>
+      <c r="Z24" s="54"/>
+      <c r="AA24" s="54"/>
+      <c r="AB24" s="54"/>
+      <c r="AC24" s="54"/>
+      <c r="AD24" s="54"/>
+      <c r="AE24" s="54"/>
     </row>
     <row r="25" spans="1:31" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C25" s="57" t="s">
+        <v>210</v>
+      </c>
+      <c r="D25" s="57" t="s">
+        <v>211</v>
+      </c>
+      <c r="E25" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="F25" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" s="57" t="s">
+        <v>213</v>
+      </c>
+      <c r="I25" s="64" t="s">
+        <v>214</v>
+      </c>
+      <c r="J25" s="59" t="s">
         <v>215</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="K25" s="74" t="s">
         <v>216</v>
       </c>
-      <c r="C25" s="60" t="s">
+      <c r="L25" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M25" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="N25" s="57" t="s">
         <v>217</v>
       </c>
-      <c r="D25" s="60" t="s">
+      <c r="O25" s="57" t="s">
         <v>218</v>
       </c>
-      <c r="E25" s="60" t="s">
-        <v>219</v>
-      </c>
-      <c r="F25" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="G25" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H25" s="60" t="s">
-        <v>220</v>
-      </c>
-      <c r="I25" s="67" t="s">
-        <v>221</v>
-      </c>
-      <c r="J25" s="62" t="s">
-        <v>222</v>
-      </c>
-      <c r="K25" s="77" t="s">
-        <v>223</v>
-      </c>
-      <c r="L25" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="M25" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="N25" s="60" t="s">
-        <v>224</v>
-      </c>
-      <c r="O25" s="60" t="s">
-        <v>225</v>
-      </c>
-      <c r="P25" s="61" t="s">
+      <c r="P25" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q25" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R25" s="64" t="s">
-        <v>214</v>
-      </c>
-      <c r="S25" s="65"/>
-      <c r="T25" s="57"/>
-      <c r="U25" s="57"/>
-      <c r="V25" s="57"/>
-      <c r="W25" s="57"/>
-      <c r="X25" s="57"/>
-      <c r="Y25" s="57"/>
-      <c r="Z25" s="57"/>
-      <c r="AA25" s="57"/>
-      <c r="AB25" s="57"/>
-      <c r="AC25" s="57"/>
-      <c r="AD25" s="57"/>
-      <c r="AE25" s="57"/>
+      <c r="Q25" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R25" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="S25" s="62"/>
+      <c r="T25" s="54"/>
+      <c r="U25" s="54"/>
+      <c r="V25" s="54"/>
+      <c r="W25" s="54"/>
+      <c r="X25" s="54"/>
+      <c r="Y25" s="54"/>
+      <c r="Z25" s="54"/>
+      <c r="AA25" s="54"/>
+      <c r="AB25" s="54"/>
+      <c r="AC25" s="54"/>
+      <c r="AD25" s="54"/>
+      <c r="AE25" s="54"/>
     </row>
     <row r="26" spans="1:31" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C26" s="57" t="s">
+        <v>221</v>
+      </c>
+      <c r="D26" s="57" t="s">
+        <v>538</v>
+      </c>
+      <c r="E26" s="75" t="s">
+        <v>537</v>
+      </c>
+      <c r="F26" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="57" t="s">
+        <v>222</v>
+      </c>
+      <c r="I26" s="64" t="s">
+        <v>546</v>
+      </c>
+      <c r="J26" s="59" t="s">
+        <v>223</v>
+      </c>
+      <c r="K26" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="L26" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M26" s="57" t="s">
+        <v>28</v>
+      </c>
+      <c r="N26" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="O26" s="57" t="s">
         <v>226</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="C26" s="60" t="s">
-        <v>228</v>
-      </c>
-      <c r="D26" s="60" t="s">
-        <v>545</v>
-      </c>
-      <c r="E26" s="78" t="s">
-        <v>544</v>
-      </c>
-      <c r="F26" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="H26" s="60" t="s">
-        <v>229</v>
-      </c>
-      <c r="I26" s="67" t="s">
-        <v>553</v>
-      </c>
-      <c r="J26" s="62" t="s">
-        <v>230</v>
-      </c>
-      <c r="K26" s="77" t="s">
-        <v>231</v>
-      </c>
-      <c r="L26" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="M26" s="60" t="s">
-        <v>28</v>
-      </c>
-      <c r="N26" s="60" t="s">
-        <v>232</v>
-      </c>
-      <c r="O26" s="60" t="s">
-        <v>233</v>
-      </c>
-      <c r="P26" s="61" t="s">
+      <c r="P26" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q26" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R26" s="64" t="s">
-        <v>214</v>
-      </c>
-      <c r="S26" s="65"/>
-      <c r="T26" s="57"/>
-      <c r="U26" s="57"/>
-      <c r="V26" s="57"/>
-      <c r="W26" s="57"/>
-      <c r="X26" s="57"/>
-      <c r="Y26" s="57"/>
-      <c r="Z26" s="57"/>
-      <c r="AA26" s="57"/>
-      <c r="AB26" s="57"/>
-      <c r="AC26" s="57"/>
-      <c r="AD26" s="57"/>
-      <c r="AE26" s="57"/>
+      <c r="Q26" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R26" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="S26" s="62"/>
+      <c r="T26" s="54"/>
+      <c r="U26" s="54"/>
+      <c r="V26" s="54"/>
+      <c r="W26" s="54"/>
+      <c r="X26" s="54"/>
+      <c r="Y26" s="54"/>
+      <c r="Z26" s="54"/>
+      <c r="AA26" s="54"/>
+      <c r="AB26" s="54"/>
+      <c r="AC26" s="54"/>
+      <c r="AD26" s="54"/>
+      <c r="AE26" s="54"/>
     </row>
     <row r="27" spans="1:31" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="C27" s="60" t="s">
         <v>228</v>
       </c>
-      <c r="D27" s="60" t="s">
-        <v>546</v>
-      </c>
-      <c r="E27" s="60" t="s">
-        <v>547</v>
-      </c>
-      <c r="F27" s="60" t="s">
+      <c r="C27" s="57" t="s">
+        <v>221</v>
+      </c>
+      <c r="D27" s="57" t="s">
+        <v>539</v>
+      </c>
+      <c r="E27" s="57" t="s">
+        <v>540</v>
+      </c>
+      <c r="F27" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="G27" s="61" t="s">
+      <c r="G27" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="H27" s="60" t="s">
+      <c r="H27" s="57" t="s">
+        <v>222</v>
+      </c>
+      <c r="I27" s="49" t="s">
+        <v>545</v>
+      </c>
+      <c r="J27" s="59" t="s">
         <v>229</v>
       </c>
-      <c r="I27" s="52" t="s">
-        <v>552</v>
-      </c>
-      <c r="J27" s="62" t="s">
-        <v>236</v>
-      </c>
-      <c r="K27" s="79" t="s">
-        <v>237</v>
-      </c>
-      <c r="L27" s="60" t="s">
+      <c r="K27" s="76" t="s">
+        <v>230</v>
+      </c>
+      <c r="L27" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M27" s="60" t="s">
+      <c r="M27" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="N27" s="60" t="s">
-        <v>238</v>
-      </c>
-      <c r="O27" s="60" t="s">
-        <v>239</v>
-      </c>
-      <c r="P27" s="61" t="s">
+      <c r="N27" s="57" t="s">
+        <v>231</v>
+      </c>
+      <c r="O27" s="57" t="s">
+        <v>232</v>
+      </c>
+      <c r="P27" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q27" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R27" s="64" t="s">
-        <v>214</v>
-      </c>
-      <c r="S27" s="65"/>
-      <c r="T27" s="57"/>
-      <c r="U27" s="57"/>
-      <c r="V27" s="57"/>
-      <c r="W27" s="57"/>
-      <c r="X27" s="57"/>
-      <c r="Y27" s="57"/>
-      <c r="Z27" s="57"/>
-      <c r="AA27" s="57"/>
-      <c r="AB27" s="57"/>
-      <c r="AC27" s="57"/>
-      <c r="AD27" s="57"/>
-      <c r="AE27" s="57"/>
+      <c r="Q27" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R27" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="S27" s="62"/>
+      <c r="T27" s="54"/>
+      <c r="U27" s="54"/>
+      <c r="V27" s="54"/>
+      <c r="W27" s="54"/>
+      <c r="X27" s="54"/>
+      <c r="Y27" s="54"/>
+      <c r="Z27" s="54"/>
+      <c r="AA27" s="54"/>
+      <c r="AB27" s="54"/>
+      <c r="AC27" s="54"/>
+      <c r="AD27" s="54"/>
+      <c r="AE27" s="54"/>
     </row>
     <row r="28" spans="1:31" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C28" s="60" t="s">
-        <v>228</v>
-      </c>
-      <c r="D28" s="60" t="s">
-        <v>548</v>
-      </c>
-      <c r="E28" s="60" t="s">
-        <v>242</v>
-      </c>
-      <c r="F28" s="60" t="s">
+        <v>234</v>
+      </c>
+      <c r="C28" s="57" t="s">
+        <v>221</v>
+      </c>
+      <c r="D28" s="57" t="s">
+        <v>541</v>
+      </c>
+      <c r="E28" s="57" t="s">
+        <v>235</v>
+      </c>
+      <c r="F28" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="G28" s="61" t="s">
+      <c r="G28" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="H28" s="60" t="s">
-        <v>229</v>
-      </c>
-      <c r="I28" s="67" t="s">
-        <v>243</v>
-      </c>
-      <c r="J28" s="62" t="s">
-        <v>230</v>
-      </c>
-      <c r="K28" s="77" t="s">
-        <v>244</v>
-      </c>
-      <c r="L28" s="60" t="s">
+      <c r="H28" s="57" t="s">
+        <v>222</v>
+      </c>
+      <c r="I28" s="64" t="s">
+        <v>236</v>
+      </c>
+      <c r="J28" s="59" t="s">
+        <v>223</v>
+      </c>
+      <c r="K28" s="74" t="s">
+        <v>237</v>
+      </c>
+      <c r="L28" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M28" s="60" t="s">
+      <c r="M28" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="N28" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="O28" s="60" t="s">
-        <v>239</v>
-      </c>
-      <c r="P28" s="61" t="s">
+      <c r="N28" s="57" t="s">
+        <v>238</v>
+      </c>
+      <c r="O28" s="57" t="s">
+        <v>232</v>
+      </c>
+      <c r="P28" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q28" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R28" s="64" t="s">
-        <v>214</v>
-      </c>
-      <c r="S28" s="65"/>
-      <c r="T28" s="57"/>
-      <c r="U28" s="57"/>
-      <c r="V28" s="57"/>
-      <c r="W28" s="57"/>
-      <c r="X28" s="57"/>
-      <c r="Y28" s="57"/>
-      <c r="Z28" s="57"/>
-      <c r="AA28" s="57"/>
-      <c r="AB28" s="57"/>
-      <c r="AC28" s="57"/>
-      <c r="AD28" s="57"/>
-      <c r="AE28" s="57"/>
+      <c r="Q28" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R28" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="S28" s="62"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="54"/>
+      <c r="W28" s="54"/>
+      <c r="X28" s="54"/>
+      <c r="Y28" s="54"/>
+      <c r="Z28" s="54"/>
+      <c r="AA28" s="54"/>
+      <c r="AB28" s="54"/>
+      <c r="AC28" s="54"/>
+      <c r="AD28" s="54"/>
+      <c r="AE28" s="54"/>
     </row>
     <row r="29" spans="1:31" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C29" s="60" t="s">
-        <v>228</v>
-      </c>
-      <c r="D29" s="60" t="s">
-        <v>549</v>
-      </c>
-      <c r="E29" s="60" t="s">
-        <v>248</v>
-      </c>
-      <c r="F29" s="60" t="s">
+        <v>240</v>
+      </c>
+      <c r="C29" s="57" t="s">
+        <v>221</v>
+      </c>
+      <c r="D29" s="57" t="s">
+        <v>542</v>
+      </c>
+      <c r="E29" s="57" t="s">
+        <v>241</v>
+      </c>
+      <c r="F29" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="G29" s="61" t="s">
+      <c r="G29" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="H29" s="60" t="s">
-        <v>229</v>
-      </c>
-      <c r="I29" s="67" t="s">
-        <v>249</v>
-      </c>
-      <c r="J29" s="62" t="s">
-        <v>230</v>
-      </c>
-      <c r="K29" s="77" t="s">
-        <v>250</v>
-      </c>
-      <c r="L29" s="60" t="s">
+      <c r="H29" s="57" t="s">
+        <v>222</v>
+      </c>
+      <c r="I29" s="64" t="s">
+        <v>242</v>
+      </c>
+      <c r="J29" s="59" t="s">
+        <v>223</v>
+      </c>
+      <c r="K29" s="74" t="s">
+        <v>243</v>
+      </c>
+      <c r="L29" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M29" s="60" t="s">
+      <c r="M29" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="N29" s="60" t="s">
-        <v>251</v>
-      </c>
-      <c r="O29" s="60" t="s">
-        <v>239</v>
-      </c>
-      <c r="P29" s="61" t="s">
+      <c r="N29" s="57" t="s">
+        <v>244</v>
+      </c>
+      <c r="O29" s="57" t="s">
+        <v>232</v>
+      </c>
+      <c r="P29" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="Q29" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R29" s="64" t="s">
-        <v>214</v>
-      </c>
-      <c r="S29" s="65"/>
-      <c r="T29" s="57"/>
-      <c r="U29" s="57"/>
-      <c r="V29" s="57"/>
-      <c r="W29" s="57"/>
-      <c r="X29" s="57"/>
-      <c r="Y29" s="57"/>
-      <c r="Z29" s="57"/>
-      <c r="AA29" s="57"/>
-      <c r="AB29" s="57"/>
-      <c r="AC29" s="57"/>
-      <c r="AD29" s="57"/>
-      <c r="AE29" s="57"/>
+      <c r="Q29" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R29" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="S29" s="62"/>
+      <c r="T29" s="54"/>
+      <c r="U29" s="54"/>
+      <c r="V29" s="54"/>
+      <c r="W29" s="54"/>
+      <c r="X29" s="54"/>
+      <c r="Y29" s="54"/>
+      <c r="Z29" s="54"/>
+      <c r="AA29" s="54"/>
+      <c r="AB29" s="54"/>
+      <c r="AC29" s="54"/>
+      <c r="AD29" s="54"/>
+      <c r="AE29" s="54"/>
     </row>
     <row r="30" spans="1:31" ht="92.4" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="C30" s="62" t="s">
-        <v>228</v>
-      </c>
-      <c r="D30" s="62" t="s">
-        <v>550</v>
-      </c>
-      <c r="E30" s="60" t="s">
-        <v>551</v>
-      </c>
-      <c r="F30" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="G30" s="62" t="s">
+        <v>246</v>
+      </c>
+      <c r="C30" s="59" t="s">
+        <v>221</v>
+      </c>
+      <c r="D30" s="59" t="s">
+        <v>543</v>
+      </c>
+      <c r="E30" s="57" t="s">
+        <v>544</v>
+      </c>
+      <c r="F30" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="H30" s="62" t="s">
-        <v>254</v>
-      </c>
-      <c r="I30" s="60" t="s">
-        <v>255</v>
-      </c>
-      <c r="J30" s="60" t="s">
-        <v>256</v>
-      </c>
-      <c r="K30" s="77" t="s">
-        <v>257</v>
-      </c>
-      <c r="L30" s="60" t="s">
+      <c r="H30" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="I30" s="57" t="s">
+        <v>248</v>
+      </c>
+      <c r="J30" s="57" t="s">
+        <v>249</v>
+      </c>
+      <c r="K30" s="74" t="s">
+        <v>250</v>
+      </c>
+      <c r="L30" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="M30" s="62" t="s">
+      <c r="M30" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="N30" s="62" t="s">
-        <v>206</v>
-      </c>
-      <c r="O30" s="60" t="s">
-        <v>206</v>
-      </c>
-      <c r="P30" s="62" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q30" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="R30" s="64" t="s">
-        <v>214</v>
-      </c>
-      <c r="S30" s="65"/>
+      <c r="N30" s="59" t="s">
+        <v>199</v>
+      </c>
+      <c r="O30" s="57" t="s">
+        <v>199</v>
+      </c>
+      <c r="P30" s="59" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q30" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R30" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="S30" s="62"/>
       <c r="T30" s="41"/>
       <c r="U30" s="41"/>
       <c r="V30" s="41"/>
@@ -5288,130 +5311,130 @@
       <c r="AE30" s="41"/>
     </row>
     <row r="31" spans="1:31" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+      <c r="A31" s="45" t="s">
+        <v>252</v>
+      </c>
+      <c r="B31" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="C31" s="77" t="s">
+        <v>198</v>
+      </c>
+      <c r="D31" s="77" t="s">
+        <v>199</v>
+      </c>
+      <c r="E31" s="77" t="s">
+        <v>254</v>
+      </c>
+      <c r="F31" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="G31" s="78" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" s="77" t="s">
+        <v>255</v>
+      </c>
+      <c r="I31" s="79" t="s">
+        <v>256</v>
+      </c>
+      <c r="J31" s="77" t="s">
+        <v>257</v>
+      </c>
+      <c r="K31" s="80" t="s">
+        <v>204</v>
+      </c>
+      <c r="L31" s="77" t="s">
+        <v>57</v>
+      </c>
+      <c r="M31" s="77" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" s="77" t="s">
+        <v>258</v>
+      </c>
+      <c r="O31" s="77" t="s">
         <v>259</v>
       </c>
-      <c r="B31" s="59" t="s">
+      <c r="P31" s="78" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q31" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R31" s="81" t="s">
+        <v>207</v>
+      </c>
+      <c r="S31" s="82"/>
+      <c r="T31" s="55"/>
+      <c r="U31" s="55"/>
+      <c r="V31" s="55"/>
+      <c r="W31" s="55"/>
+      <c r="X31" s="55"/>
+      <c r="Y31" s="55"/>
+      <c r="Z31" s="55"/>
+      <c r="AA31" s="55"/>
+      <c r="AB31" s="55"/>
+      <c r="AC31" s="55"/>
+      <c r="AD31" s="55"/>
+      <c r="AE31" s="55"/>
+    </row>
+    <row r="32" spans="1:31" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="46" t="s">
         <v>260</v>
       </c>
-      <c r="C31" s="80" t="s">
-        <v>205</v>
-      </c>
-      <c r="D31" s="80" t="s">
-        <v>206</v>
-      </c>
-      <c r="E31" s="80" t="s">
+      <c r="B32" s="47" t="s">
         <v>261</v>
       </c>
-      <c r="F31" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="G31" s="81" t="s">
+      <c r="C32" s="71" t="s">
+        <v>262</v>
+      </c>
+      <c r="D32" s="71" t="s">
+        <v>263</v>
+      </c>
+      <c r="E32" s="83" t="s">
+        <v>532</v>
+      </c>
+      <c r="F32" s="84" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="H31" s="80" t="s">
-        <v>262</v>
-      </c>
-      <c r="I31" s="82" t="s">
-        <v>263</v>
-      </c>
-      <c r="J31" s="80" t="s">
+      <c r="H32" s="71" t="s">
         <v>264</v>
       </c>
-      <c r="K31" s="83" t="s">
-        <v>211</v>
-      </c>
-      <c r="L31" s="80" t="s">
-        <v>58</v>
-      </c>
-      <c r="M31" s="80" t="s">
-        <v>59</v>
-      </c>
-      <c r="N31" s="80" t="s">
+      <c r="I32" s="83" t="s">
         <v>265</v>
       </c>
-      <c r="O31" s="80" t="s">
+      <c r="J32" s="83" t="s">
         <v>266</v>
       </c>
-      <c r="P31" s="81" t="s">
+      <c r="K32" s="85" t="s">
+        <v>267</v>
+      </c>
+      <c r="L32" s="83" t="s">
+        <v>57</v>
+      </c>
+      <c r="M32" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="N32" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="O32" s="83" t="s">
+        <v>269</v>
+      </c>
+      <c r="P32" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="Q31" s="84" t="s">
-        <v>33</v>
-      </c>
-      <c r="R31" s="85" t="s">
-        <v>214</v>
-      </c>
-      <c r="S31" s="86"/>
-      <c r="T31" s="58"/>
-      <c r="U31" s="58"/>
-      <c r="V31" s="58"/>
-      <c r="W31" s="58"/>
-      <c r="X31" s="58"/>
-      <c r="Y31" s="58"/>
-      <c r="Z31" s="58"/>
-      <c r="AA31" s="58"/>
-      <c r="AB31" s="58"/>
-      <c r="AC31" s="58"/>
-      <c r="AD31" s="58"/>
-      <c r="AE31" s="58"/>
-    </row>
-    <row r="32" spans="1:31" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="48" t="s">
-        <v>267</v>
-      </c>
-      <c r="B32" s="49" t="s">
-        <v>268</v>
-      </c>
-      <c r="C32" s="74" t="s">
-        <v>269</v>
-      </c>
-      <c r="D32" s="74" t="s">
-        <v>270</v>
-      </c>
-      <c r="E32" s="87" t="s">
-        <v>539</v>
-      </c>
-      <c r="F32" s="88" t="s">
-        <v>24</v>
-      </c>
-      <c r="G32" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="H32" s="74" t="s">
-        <v>271</v>
-      </c>
-      <c r="I32" s="87" t="s">
-        <v>272</v>
-      </c>
-      <c r="J32" s="87" t="s">
-        <v>273</v>
-      </c>
-      <c r="K32" s="89" t="s">
-        <v>274</v>
-      </c>
-      <c r="L32" s="87" t="s">
-        <v>58</v>
-      </c>
-      <c r="M32" s="74" t="s">
-        <v>28</v>
-      </c>
-      <c r="N32" s="74" t="s">
-        <v>275</v>
-      </c>
-      <c r="O32" s="87" t="s">
-        <v>276</v>
-      </c>
-      <c r="P32" s="74" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q32" s="90" t="s">
-        <v>33</v>
-      </c>
-      <c r="R32" s="91" t="s">
-        <v>214</v>
-      </c>
-      <c r="S32" s="65"/>
+      <c r="Q32" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R32" s="86" t="s">
+        <v>207</v>
+      </c>
+      <c r="S32" s="62"/>
       <c r="T32" s="41"/>
       <c r="U32" s="41"/>
       <c r="V32" s="41"/>
@@ -5426,55 +5449,55 @@
       <c r="AE32" s="41"/>
     </row>
     <row r="33" spans="1:31" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A33" s="44" t="s">
-        <v>515</v>
-      </c>
-      <c r="B33" s="45" t="s">
-        <v>520</v>
-      </c>
-      <c r="C33" s="66"/>
-      <c r="D33" s="92" t="s">
-        <v>531</v>
-      </c>
-      <c r="E33" s="93" t="s">
-        <v>532</v>
-      </c>
-      <c r="F33" s="86" t="s">
-        <v>39</v>
-      </c>
-      <c r="G33" s="66" t="s">
+      <c r="A33" s="43" t="s">
+        <v>508</v>
+      </c>
+      <c r="B33" s="44" t="s">
+        <v>513</v>
+      </c>
+      <c r="C33" s="63"/>
+      <c r="D33" s="87" t="s">
+        <v>524</v>
+      </c>
+      <c r="E33" s="88" t="s">
+        <v>525</v>
+      </c>
+      <c r="F33" s="82" t="s">
+        <v>38</v>
+      </c>
+      <c r="G33" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="H33" s="66"/>
-      <c r="I33" s="93" t="s">
-        <v>537</v>
-      </c>
-      <c r="J33" s="94" t="s">
-        <v>520</v>
-      </c>
-      <c r="K33" s="66"/>
-      <c r="L33" s="65" t="s">
+      <c r="H33" s="63"/>
+      <c r="I33" s="88" t="s">
+        <v>530</v>
+      </c>
+      <c r="J33" s="89" t="s">
+        <v>513</v>
+      </c>
+      <c r="K33" s="63"/>
+      <c r="L33" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="M33" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="M33" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="N33" s="66" t="s">
-        <v>521</v>
-      </c>
-      <c r="O33" s="94" t="s">
-        <v>543</v>
-      </c>
-      <c r="P33" s="66" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q33" s="90" t="s">
+      <c r="N33" s="63" t="s">
+        <v>514</v>
+      </c>
+      <c r="O33" s="89" t="s">
+        <v>536</v>
+      </c>
+      <c r="P33" s="63" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q33" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R33" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="R33" s="95" t="s">
-        <v>34</v>
-      </c>
-      <c r="S33" s="65"/>
+      <c r="S33" s="62"/>
       <c r="T33" s="41"/>
       <c r="U33" s="41"/>
       <c r="V33" s="41"/>
@@ -5489,55 +5512,55 @@
       <c r="AE33" s="41"/>
     </row>
     <row r="34" spans="1:31" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A34" s="44" t="s">
-        <v>516</v>
-      </c>
-      <c r="B34" s="51" t="s">
+      <c r="A34" s="43" t="s">
+        <v>509</v>
+      </c>
+      <c r="B34" s="48" t="s">
+        <v>519</v>
+      </c>
+      <c r="C34" s="63"/>
+      <c r="D34" s="91" t="s">
+        <v>524</v>
+      </c>
+      <c r="E34" s="92" t="s">
         <v>526</v>
       </c>
-      <c r="C34" s="66"/>
-      <c r="D34" s="96" t="s">
+      <c r="F34" s="82" t="s">
+        <v>38</v>
+      </c>
+      <c r="G34" s="63" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34" s="63"/>
+      <c r="I34" s="92" t="s">
         <v>531</v>
       </c>
-      <c r="E34" s="97" t="s">
+      <c r="J34" s="92" t="s">
         <v>533</v>
       </c>
-      <c r="F34" s="86" t="s">
-        <v>39</v>
-      </c>
-      <c r="G34" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="H34" s="66"/>
-      <c r="I34" s="97" t="s">
-        <v>538</v>
-      </c>
-      <c r="J34" s="97" t="s">
-        <v>540</v>
-      </c>
-      <c r="K34" s="66"/>
-      <c r="L34" s="65" t="s">
+      <c r="K34" s="63"/>
+      <c r="L34" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="M34" s="66" t="s">
+      <c r="M34" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="N34" s="66" t="s">
-        <v>522</v>
-      </c>
-      <c r="O34" s="94" t="s">
-        <v>543</v>
-      </c>
-      <c r="P34" s="66" t="s">
+      <c r="N34" s="63" t="s">
+        <v>515</v>
+      </c>
+      <c r="O34" s="89" t="s">
+        <v>536</v>
+      </c>
+      <c r="P34" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="Q34" s="90" t="s">
+      <c r="Q34" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R34" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="R34" s="95" t="s">
-        <v>34</v>
-      </c>
-      <c r="S34" s="65"/>
+      <c r="S34" s="62"/>
       <c r="T34" s="41"/>
       <c r="U34" s="41"/>
       <c r="V34" s="41"/>
@@ -5552,55 +5575,55 @@
       <c r="AE34" s="41"/>
     </row>
     <row r="35" spans="1:31" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A35" s="44" t="s">
-        <v>517</v>
-      </c>
-      <c r="B35" s="51" t="s">
-        <v>528</v>
-      </c>
-      <c r="C35" s="66"/>
-      <c r="D35" s="92" t="s">
-        <v>531</v>
-      </c>
-      <c r="E35" s="94" t="s">
-        <v>534</v>
-      </c>
-      <c r="F35" s="86" t="s">
-        <v>39</v>
-      </c>
-      <c r="G35" s="66" t="s">
+      <c r="A35" s="43" t="s">
+        <v>510</v>
+      </c>
+      <c r="B35" s="48" t="s">
+        <v>521</v>
+      </c>
+      <c r="C35" s="63"/>
+      <c r="D35" s="87" t="s">
+        <v>524</v>
+      </c>
+      <c r="E35" s="89" t="s">
+        <v>527</v>
+      </c>
+      <c r="F35" s="82" t="s">
+        <v>38</v>
+      </c>
+      <c r="G35" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="H35" s="66"/>
-      <c r="I35" s="94" t="s">
-        <v>263</v>
-      </c>
-      <c r="J35" s="94" t="s">
-        <v>527</v>
-      </c>
-      <c r="K35" s="66"/>
-      <c r="L35" s="65" t="s">
+      <c r="H35" s="63"/>
+      <c r="I35" s="89" t="s">
+        <v>256</v>
+      </c>
+      <c r="J35" s="89" t="s">
+        <v>520</v>
+      </c>
+      <c r="K35" s="63"/>
+      <c r="L35" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="M35" s="66" t="s">
+      <c r="M35" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="N35" s="66" t="s">
-        <v>523</v>
-      </c>
-      <c r="O35" s="94" t="s">
-        <v>543</v>
-      </c>
-      <c r="P35" s="66" t="s">
+      <c r="N35" s="63" t="s">
+        <v>516</v>
+      </c>
+      <c r="O35" s="89" t="s">
+        <v>536</v>
+      </c>
+      <c r="P35" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="Q35" s="90" t="s">
+      <c r="Q35" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R35" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="R35" s="95" t="s">
-        <v>34</v>
-      </c>
-      <c r="S35" s="65"/>
+      <c r="S35" s="62"/>
       <c r="T35" s="41"/>
       <c r="U35" s="41"/>
       <c r="V35" s="41"/>
@@ -5615,55 +5638,55 @@
       <c r="AE35" s="41"/>
     </row>
     <row r="36" spans="1:31" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A36" s="44" t="s">
-        <v>518</v>
-      </c>
-      <c r="B36" s="51" t="s">
-        <v>529</v>
-      </c>
-      <c r="C36" s="66"/>
-      <c r="D36" s="96" t="s">
-        <v>531</v>
-      </c>
-      <c r="E36" s="97" t="s">
-        <v>535</v>
-      </c>
-      <c r="F36" s="86" t="s">
-        <v>39</v>
-      </c>
-      <c r="G36" s="66" t="s">
+      <c r="A36" s="43" t="s">
+        <v>511</v>
+      </c>
+      <c r="B36" s="48" t="s">
+        <v>522</v>
+      </c>
+      <c r="C36" s="63"/>
+      <c r="D36" s="91" t="s">
+        <v>524</v>
+      </c>
+      <c r="E36" s="92" t="s">
+        <v>528</v>
+      </c>
+      <c r="F36" s="82" t="s">
+        <v>38</v>
+      </c>
+      <c r="G36" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="H36" s="66"/>
-      <c r="I36" s="97" t="s">
-        <v>263</v>
-      </c>
-      <c r="J36" s="97" t="s">
-        <v>541</v>
-      </c>
-      <c r="K36" s="66"/>
-      <c r="L36" s="65" t="s">
+      <c r="H36" s="63"/>
+      <c r="I36" s="92" t="s">
+        <v>256</v>
+      </c>
+      <c r="J36" s="92" t="s">
+        <v>534</v>
+      </c>
+      <c r="K36" s="63"/>
+      <c r="L36" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="M36" s="66" t="s">
+      <c r="M36" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="N36" s="66" t="s">
-        <v>524</v>
-      </c>
-      <c r="O36" s="94" t="s">
-        <v>543</v>
-      </c>
-      <c r="P36" s="66" t="s">
+      <c r="N36" s="63" t="s">
+        <v>517</v>
+      </c>
+      <c r="O36" s="89" t="s">
+        <v>536</v>
+      </c>
+      <c r="P36" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="Q36" s="90" t="s">
+      <c r="Q36" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R36" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="R36" s="95" t="s">
-        <v>34</v>
-      </c>
-      <c r="S36" s="65"/>
+      <c r="S36" s="62"/>
       <c r="T36" s="41"/>
       <c r="U36" s="41"/>
       <c r="V36" s="41"/>
@@ -5678,55 +5701,55 @@
       <c r="AE36" s="41"/>
     </row>
     <row r="37" spans="1:31" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A37" s="44" t="s">
-        <v>519</v>
-      </c>
-      <c r="B37" s="51" t="s">
-        <v>530</v>
-      </c>
-      <c r="C37" s="66"/>
-      <c r="D37" s="92" t="s">
-        <v>531</v>
-      </c>
-      <c r="E37" s="94" t="s">
+      <c r="A37" s="43" t="s">
+        <v>512</v>
+      </c>
+      <c r="B37" s="48" t="s">
+        <v>523</v>
+      </c>
+      <c r="C37" s="63"/>
+      <c r="D37" s="87" t="s">
+        <v>524</v>
+      </c>
+      <c r="E37" s="89" t="s">
+        <v>529</v>
+      </c>
+      <c r="F37" s="82" t="s">
+        <v>38</v>
+      </c>
+      <c r="G37" s="63" t="s">
+        <v>25</v>
+      </c>
+      <c r="H37" s="63"/>
+      <c r="I37" s="89" t="s">
+        <v>256</v>
+      </c>
+      <c r="J37" s="93" t="s">
+        <v>535</v>
+      </c>
+      <c r="K37" s="63"/>
+      <c r="L37" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="M37" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="N37" s="63" t="s">
+        <v>518</v>
+      </c>
+      <c r="O37" s="89" t="s">
         <v>536</v>
       </c>
-      <c r="F37" s="86" t="s">
-        <v>39</v>
-      </c>
-      <c r="G37" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="H37" s="66"/>
-      <c r="I37" s="94" t="s">
-        <v>263</v>
-      </c>
-      <c r="J37" s="98" t="s">
-        <v>542</v>
-      </c>
-      <c r="K37" s="66"/>
-      <c r="L37" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="M37" s="66" t="s">
-        <v>28</v>
-      </c>
-      <c r="N37" s="66" t="s">
-        <v>525</v>
-      </c>
-      <c r="O37" s="94" t="s">
-        <v>543</v>
-      </c>
-      <c r="P37" s="66" t="s">
+      <c r="P37" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="Q37" s="90" t="s">
+      <c r="Q37" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R37" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="R37" s="95" t="s">
-        <v>34</v>
-      </c>
-      <c r="S37" s="65"/>
+      <c r="S37" s="62"/>
       <c r="T37" s="41"/>
       <c r="U37" s="41"/>
       <c r="V37" s="41"/>
@@ -5740,26 +5763,56 @@
       <c r="AD37" s="41"/>
       <c r="AE37" s="41"/>
     </row>
-    <row r="38" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="41"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="42"/>
-      <c r="J38" s="42"/>
-      <c r="K38" s="41"/>
-      <c r="L38" s="41"/>
-      <c r="M38" s="41"/>
-      <c r="N38" s="41"/>
-      <c r="O38" s="42"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
-      <c r="S38" s="42"/>
+    <row r="38" spans="1:31" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A38" s="95" t="s">
+        <v>555</v>
+      </c>
+      <c r="B38" s="96" t="s">
+        <v>556</v>
+      </c>
+      <c r="C38" s="63" t="s">
+        <v>557</v>
+      </c>
+      <c r="D38" s="87"/>
+      <c r="E38" s="89" t="s">
+        <v>558</v>
+      </c>
+      <c r="F38" s="82" t="s">
+        <v>24</v>
+      </c>
+      <c r="G38" s="63" t="s">
+        <v>25</v>
+      </c>
+      <c r="H38" s="63"/>
+      <c r="I38" s="89" t="s">
+        <v>559</v>
+      </c>
+      <c r="J38" s="93" t="s">
+        <v>560</v>
+      </c>
+      <c r="K38" s="63"/>
+      <c r="L38" s="97" t="s">
+        <v>28</v>
+      </c>
+      <c r="M38" s="63" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" s="63" t="s">
+        <v>518</v>
+      </c>
+      <c r="O38" s="89" t="s">
+        <v>561</v>
+      </c>
+      <c r="P38" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q38" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="R38" s="90" t="s">
+        <v>562</v>
+      </c>
+      <c r="S38" s="62"/>
       <c r="T38" s="41"/>
       <c r="U38" s="41"/>
       <c r="V38" s="41"/>
@@ -37389,31 +37442,36 @@
     </row>
   </sheetData>
   <phoneticPr fontId="22" type="noConversion"/>
-  <conditionalFormatting sqref="Q2:Q30">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="New">
+  <conditionalFormatting sqref="Q2:Q38">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="New">
       <formula>NOT(ISERROR(SEARCH(("New"),(Q2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="New">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="New">
       <formula>NOT(ISERROR(SEARCH(("New"),(Q2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Closed">
+    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="Closed">
       <formula>NOT(ISERROR(SEARCH(("Closed"),(Q2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Fix">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Fix">
       <formula>NOT(ISERROR(SEARCH(("Fix"),(Q2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Reopen">
+    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="Reopen">
       <formula>NOT(ISERROR(SEARCH(("Reopen"),(Q2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="Open">
+    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="Open">
       <formula>NOT(ISERROR(SEARCH(("Open"),(Q2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="Reopen">
+    <cfRule type="containsText" dxfId="1" priority="8" operator="containsText" text="Reopen">
       <formula>NOT(ISERROR(SEARCH(("Reopen"),(Q2))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q2:Q37" xr:uid="{00000000-0002-0000-0000-000001000000}">
+  <conditionalFormatting sqref="Q16">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Not a Bug">
+      <formula>NOT(ISERROR(SEARCH("Not a Bug",Q16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q2:Q15 Q17:Q38" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"New,Open,Fix,Reopen,Closed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:L34" xr:uid="{00000000-0002-0000-0000-000002000000}">
@@ -37422,7 +37480,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R32" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Mahmoud,jana,Fatma"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P2:P37" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P2:P38" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Functional,Functional/UI"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M2:M34" xr:uid="{00000000-0002-0000-0000-000005000000}">
@@ -37430,6 +37488,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F38" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"valid,invalid"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Q16" xr:uid="{4D9F7D5C-A39C-4157-8025-43AF83578535}">
+      <formula1>"New,Open,Fix,Reopen,Closed, Not a Bug"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -37472,16 +37533,16 @@
   <sheetData>
     <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>2</v>
@@ -37493,16 +37554,16 @@
         <v>3</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="L1" s="14" t="s">
         <v>10</v>
@@ -37514,60 +37575,60 @@
         <v>15</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="P1" s="14" t="s">
         <v>18</v>
       </c>
       <c r="Q1" s="15" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" s="16" t="s">
         <v>287</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>294</v>
       </c>
       <c r="J2" s="8"/>
       <c r="K2" s="8" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L2" s="8"/>
       <c r="M2" s="8" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="P2" s="8"/>
       <c r="Q2" s="8" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="R2" s="8"/>
       <c r="S2" s="8"/>
@@ -37584,49 +37645,49 @@
     </row>
     <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="8" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L3" s="8"/>
       <c r="M3" s="8" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="P3" s="8"/>
       <c r="Q3" s="8" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
@@ -37643,49 +37704,49 @@
     </row>
     <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="F4" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="G4" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="G4" s="16" t="s">
-        <v>310</v>
-      </c>
       <c r="H4" s="16" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="8" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L4" s="8"/>
       <c r="M4" s="8" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="P4" s="8"/>
       <c r="Q4" s="8" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="R4" s="8"/>
       <c r="S4" s="8"/>
@@ -37702,49 +37763,49 @@
     </row>
     <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="8" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L5" s="8"/>
       <c r="M5" s="8" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="P5" s="8"/>
       <c r="Q5" s="8" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="R5" s="8"/>
       <c r="S5" s="8"/>
@@ -37761,49 +37822,49 @@
     </row>
     <row r="6" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>24</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L6" s="18"/>
       <c r="M6" s="18" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="N6" s="18" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O6" s="18" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="P6" s="18"/>
       <c r="Q6" s="8" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="R6" s="18"/>
       <c r="S6" s="18"/>
@@ -37820,49 +37881,49 @@
     </row>
     <row r="7" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="8" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
@@ -37879,49 +37940,49 @@
     </row>
     <row r="8" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L8" s="8"/>
       <c r="M8" s="8" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="P8" s="8"/>
       <c r="Q8" s="8" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="R8" s="8"/>
       <c r="S8" s="8"/>
@@ -37938,49 +37999,49 @@
     </row>
     <row r="9" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J9" s="18"/>
       <c r="K9" s="18" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L9" s="18"/>
       <c r="M9" s="18" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="P9" s="18"/>
       <c r="Q9" s="8" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="R9" s="18"/>
       <c r="S9" s="18"/>
@@ -37997,47 +38058,47 @@
     </row>
     <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="I10" s="21"/>
       <c r="J10" s="21"/>
       <c r="K10" s="21" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L10" s="21"/>
       <c r="M10" s="23" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="N10" s="21" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O10" s="23" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="P10" s="21"/>
       <c r="Q10" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="R10" s="21"/>
       <c r="S10" s="21"/>
@@ -38054,47 +38115,47 @@
     </row>
     <row r="11" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C11" s="22" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="F11" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="G11" s="21" t="s">
         <v>342</v>
       </c>
-      <c r="G11" s="21" t="s">
-        <v>349</v>
-      </c>
       <c r="H11" s="23" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="I11" s="21"/>
       <c r="J11" s="21"/>
       <c r="K11" s="21" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L11" s="21"/>
       <c r="M11" s="23" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="N11" s="21" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O11" s="23" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="P11" s="21"/>
       <c r="Q11" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="R11" s="21"/>
       <c r="S11" s="21"/>
@@ -38111,47 +38172,47 @@
     </row>
     <row r="12" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="I12" s="21"/>
       <c r="J12" s="21"/>
       <c r="K12" s="21" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L12" s="21"/>
       <c r="M12" s="23" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="N12" s="21" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O12" s="23" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="P12" s="21"/>
       <c r="Q12" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="R12" s="21"/>
       <c r="S12" s="21"/>
@@ -38168,47 +38229,47 @@
     </row>
     <row r="13" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="I13" s="21"/>
       <c r="J13" s="21"/>
       <c r="K13" s="21" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="23" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="N13" s="21" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O13" s="23" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="P13" s="21"/>
       <c r="Q13" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="R13" s="21"/>
       <c r="S13" s="21"/>
@@ -38225,47 +38286,47 @@
     </row>
     <row r="14" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="I14" s="21"/>
       <c r="J14" s="21"/>
       <c r="K14" s="21" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L14" s="21"/>
       <c r="M14" s="23" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="N14" s="21" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O14" s="23" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="P14" s="21"/>
       <c r="Q14" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="R14" s="21"/>
       <c r="S14" s="21"/>
@@ -38282,47 +38343,47 @@
     </row>
     <row r="15" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="I15" s="21"/>
       <c r="J15" s="21"/>
       <c r="K15" s="21" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L15" s="21"/>
       <c r="M15" s="23" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="N15" s="21" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O15" s="23" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="P15" s="21"/>
       <c r="Q15" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="R15" s="21"/>
       <c r="S15" s="21"/>
@@ -38339,47 +38400,47 @@
     </row>
     <row r="16" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="I16" s="21"/>
       <c r="J16" s="21"/>
       <c r="K16" s="21" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L16" s="21"/>
       <c r="M16" s="23" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="N16" s="21" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O16" s="23" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="P16" s="21"/>
       <c r="Q16" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="R16" s="21"/>
       <c r="S16" s="21"/>
@@ -38396,192 +38457,192 @@
     </row>
     <row r="17" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="M17" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="N17" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="O17" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="F17" s="10" t="s">
+      <c r="Q17" s="8" t="s">
         <v>371</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="L17" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="M17" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="N17" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="O17" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="Q17" s="8" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="18" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="M18" s="13" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="O18" s="13" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="O19" s="13" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="I20" s="24"/>
       <c r="J20" s="24" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="K20" s="24" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L20" s="24" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="M20" s="25" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="N20" s="24" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O20" s="13" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="P20" s="24"/>
       <c r="Q20" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="R20" s="24"/>
       <c r="S20" s="24"/>
@@ -38598,51 +38659,51 @@
     </row>
     <row r="21" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="G21" s="28" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="H21" s="26" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L21" s="9"/>
       <c r="M21" s="29" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="N21" s="26" t="s">
         <v>32</v>
       </c>
       <c r="O21" s="27" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="P21" s="30" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="Q21" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="R21" s="9"/>
       <c r="S21" s="9"/>
@@ -38659,237 +38720,237 @@
     </row>
     <row r="22" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="H22" s="31" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O22" s="13" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="P22" s="30" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="Q22" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="23" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="F23" s="32" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O23" s="13" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="P23" s="30" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="24" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O24" s="13"/>
       <c r="P24" s="30" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="25" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O25" s="13" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="P25" s="30" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>24</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="F26" s="33" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="J26" s="24"/>
       <c r="K26" s="24" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L26" s="24"/>
       <c r="M26" s="25" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="N26" s="24" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O26" s="25" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="P26" s="30" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="R26" s="24"/>
       <c r="S26" s="24"/>
@@ -38906,336 +38967,336 @@
     </row>
     <row r="27" spans="1:29" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D27" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="M27" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="N27" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="O27" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="E27" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="M27" s="13" t="s">
-        <v>440</v>
-      </c>
-      <c r="N27" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="O27" s="13" t="s">
-        <v>442</v>
-      </c>
       <c r="Q27" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="1:29" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="N28" s="10" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="O28" s="13" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="M29" s="13" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="O29" s="13" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="Q29" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="H30" s="31" t="s">
+        <v>455</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="M30" s="13" t="s">
         <v>456</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="O30" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>458</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>461</v>
-      </c>
-      <c r="H30" s="31" t="s">
-        <v>462</v>
-      </c>
-      <c r="K30" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="M30" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="O30" s="13" t="s">
-        <v>464</v>
-      </c>
       <c r="Q30" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="H31" s="31" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="O31" s="13" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="Q31" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="H32" s="31" t="s">
+        <v>468</v>
+      </c>
+      <c r="I32" s="34" t="s">
+        <v>468</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="M32" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="O32" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>471</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>473</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>474</v>
-      </c>
-      <c r="H32" s="31" t="s">
-        <v>475</v>
-      </c>
-      <c r="I32" s="34" t="s">
-        <v>475</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="M32" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="O32" s="13" t="s">
-        <v>476</v>
-      </c>
       <c r="Q32" s="8" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="G33" s="35" t="s">
+        <v>475</v>
+      </c>
+      <c r="H33" s="31" t="s">
+        <v>476</v>
+      </c>
+      <c r="J33" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="K33" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="M33" s="13" t="s">
         <v>478</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="10" t="s">
+      <c r="N33" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="O33" s="13" t="s">
         <v>479</v>
       </c>
-      <c r="E33" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="G33" s="35" t="s">
-        <v>482</v>
-      </c>
-      <c r="H33" s="31" t="s">
-        <v>483</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>484</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="M33" s="13" t="s">
-        <v>485</v>
-      </c>
-      <c r="N33" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="O33" s="13" t="s">
-        <v>486</v>
-      </c>
       <c r="Q33" s="8" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:29" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="G34" s="36" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="I34" s="36"/>
       <c r="J34" s="36" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L34" s="36"/>
       <c r="M34" s="38" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="N34" s="36" t="s">
         <v>32</v>
       </c>
       <c r="O34" s="37" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="P34" s="36"/>
       <c r="Q34" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="R34" s="36"/>
       <c r="S34" s="36"/>
@@ -39252,49 +39313,49 @@
     </row>
     <row r="35" spans="1:29" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="36" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E35" s="36" t="s">
+        <v>482</v>
+      </c>
+      <c r="F35" s="36" t="s">
+        <v>483</v>
+      </c>
+      <c r="G35" s="36" t="s">
         <v>489</v>
       </c>
-      <c r="F35" s="36" t="s">
-        <v>490</v>
-      </c>
-      <c r="G35" s="36" t="s">
-        <v>496</v>
-      </c>
       <c r="H35" s="37" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="I35" s="36"/>
       <c r="J35" s="36" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L35" s="36"/>
       <c r="M35" s="38" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="N35" s="36" t="s">
         <v>32</v>
       </c>
       <c r="O35" s="37" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="P35" s="36"/>
       <c r="Q35" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="R35" s="36"/>
       <c r="S35" s="36"/>
@@ -39311,93 +39372,93 @@
     </row>
     <row r="36" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E36" s="39" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="M36" s="35" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="N36" s="10" t="s">
         <v>32</v>
       </c>
       <c r="O36" s="13" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="Q36" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="36" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D37" s="36" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E37" s="34" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="G37" s="36" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="H37" s="40" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="I37" s="36"/>
       <c r="J37" s="36" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L37" s="36"/>
       <c r="M37" s="38" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="N37" s="36" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O37" s="37" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="P37" s="36"/>
       <c r="Q37" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="R37" s="36"/>
       <c r="S37" s="36"/>
@@ -39414,49 +39475,49 @@
     </row>
     <row r="38" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D38" s="36" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E38" s="34" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="G38" s="36" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="H38" s="40" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="I38" s="36"/>
       <c r="J38" s="36" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="K38" s="36" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="L38" s="36"/>
       <c r="M38" s="38" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="N38" s="36" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O38" s="37" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="P38" s="36"/>
       <c r="Q38" s="8" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="R38" s="36"/>
       <c r="S38" s="36"/>
